--- a/src/attributions/attributions_saliency_traj_181.xlsx
+++ b/src/attributions/attributions_saliency_traj_181.xlsx
@@ -999,1140 +999,1140 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.06732848286628723</v>
+        <v>0.02096562460064888</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3833684027194977</v>
+        <v>0.2845205962657928</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03323633223772049</v>
+        <v>0.05885419622063637</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1897079348564148</v>
+        <v>0.2752969861030579</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05082228034734726</v>
+        <v>0.004334054887294769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1161199808120728</v>
+        <v>0.0990324467420578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00679634977132082</v>
+        <v>0.1850683689117432</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009218074381351471</v>
+        <v>0.04690198227763176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007331374101340771</v>
+        <v>0.07129733264446259</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08441610634326935</v>
+        <v>0.06870134174823761</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2655494213104248</v>
+        <v>0.242415264248848</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006758969277143478</v>
+        <v>0.03261023014783859</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1580517888069153</v>
+        <v>0.4353302121162415</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07448375225067139</v>
+        <v>0.05232694745063782</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1549170464277267</v>
+        <v>0.03493474051356316</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02542304247617722</v>
+        <v>0.167111873626709</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06463027000427246</v>
+        <v>0.1364674121141434</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0189715251326561</v>
+        <v>0.003056198358535767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01012525986880064</v>
+        <v>0.005181066691875458</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03249503672122955</v>
+        <v>0.0791122168302536</v>
       </c>
       <c r="U2" t="n">
-        <v>0.007066601421684027</v>
+        <v>0.07969273626804352</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0475337840616703</v>
+        <v>0.03063002415001392</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01626153476536274</v>
+        <v>0.02774623222649097</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03990303725004196</v>
+        <v>0.08013054728507996</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04490857571363449</v>
+        <v>0.01541703473776579</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01595618389546871</v>
+        <v>0.005830502137541771</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03869836777448654</v>
+        <v>0.09292590618133545</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01232240907847881</v>
+        <v>0.02638881094753742</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.02305964194238186</v>
+        <v>0.1167817413806915</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.01749424077570438</v>
+        <v>0.08137813955545425</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001573490910232067</v>
+        <v>0.07986541837453842</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.02526273019611835</v>
+        <v>0.08020725846290588</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.01750597171485424</v>
+        <v>0.0831129252910614</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.01534902583807707</v>
+        <v>0.0269622914493084</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.003327714279294014</v>
+        <v>0.02627245336771011</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.02190300449728966</v>
+        <v>0.06370998173952103</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01954901963472366</v>
+        <v>0.0322662889957428</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03966275230050087</v>
+        <v>0.2018925398588181</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.009013538248836994</v>
+        <v>0.00948051642626524</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.004835980013012886</v>
+        <v>0.04635417461395264</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.007245868444442749</v>
+        <v>0.2944535613059998</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.03233620151877403</v>
+        <v>0.09743157029151917</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.02240126579999924</v>
+        <v>0.05112426728010178</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01308237668126822</v>
+        <v>0.07399634271860123</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.03119565546512604</v>
+        <v>0.01830938458442688</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.009813357144594193</v>
+        <v>0.02219985798001289</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2366055846214294</v>
+        <v>0.2577478289604187</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.002072746865451336</v>
+        <v>0.008984344080090523</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.04581477120518684</v>
+        <v>0.1565379798412323</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0103433346375823</v>
+        <v>0.08658613264560699</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.01220745779573917</v>
+        <v>0.02181690186262131</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01113699190318584</v>
+        <v>0.007214797660708427</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.01091498509049416</v>
+        <v>0.02088057994842529</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.03691761940717697</v>
+        <v>0.08021989464759827</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.04276542738080025</v>
+        <v>0.1060435548424721</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.06935586780309677</v>
+        <v>0.1559779793024063</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.07099087536334991</v>
+        <v>0.1035407036542892</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.04113011062145233</v>
+        <v>0.02728946506977081</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.08598208427429199</v>
+        <v>0.1021680757403374</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.07607807964086533</v>
+        <v>0.1112546026706696</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.003672536462545395</v>
+        <v>0.1371930092573166</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.04837565869092941</v>
+        <v>0.06457673013210297</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.01282848976552486</v>
+        <v>0.1556355208158493</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.05987945571541786</v>
+        <v>0.01027835346758366</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.02228167094290257</v>
+        <v>0.09974785149097443</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.009851875714957714</v>
+        <v>0.02879880741238594</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.02387160249054432</v>
+        <v>0.03599535301327705</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.004714064300060272</v>
+        <v>0.08833310008049011</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.01995285227894783</v>
+        <v>0.05635632574558258</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.007761510089039803</v>
+        <v>0.02053486369550228</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.004707099869847298</v>
+        <v>0.013610546477139</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.006732623092830181</v>
+        <v>0.007179977372288704</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.004047682508826256</v>
+        <v>0.01261135004460812</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1201156005263329</v>
+        <v>0.191620722413063</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0141333369538188</v>
+        <v>0.03477432578802109</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.03090335614979267</v>
+        <v>0.196945995092392</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.004812256898730993</v>
+        <v>0.03426322340965271</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.06224995106458664</v>
+        <v>0.02693776600062847</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.03115922026336193</v>
+        <v>0.02688162215054035</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.01669177785515785</v>
+        <v>0.00750492699444294</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.02926177345216274</v>
+        <v>0.06380996853113174</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0260192509740591</v>
+        <v>0.01585796289145947</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.05923766270279884</v>
+        <v>0.1435790956020355</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.02254578471183777</v>
+        <v>0.009137393906712532</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.02004878222942352</v>
+        <v>0.1598502546548843</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.02050838246941566</v>
+        <v>0.03826484829187393</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.03228957578539848</v>
+        <v>0.002014327794313431</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.008156619034707546</v>
+        <v>0.003199566621333361</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.001806535758078098</v>
+        <v>0.05792262777686119</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.02039400860667229</v>
+        <v>0.02970029413700104</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.004045804962515831</v>
+        <v>0.0808873176574707</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.009953796863555908</v>
+        <v>0.139614924788475</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.004111483693122864</v>
+        <v>0.08565534651279449</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.04477573186159134</v>
+        <v>0.4819955825805664</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.03606287389993668</v>
+        <v>0.0673622339963913</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.02634396404027939</v>
+        <v>0.08406960219144821</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.04615515097975731</v>
+        <v>0.02243326604366302</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.05629439651966095</v>
+        <v>0.01365416217595339</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.009366807527840137</v>
+        <v>0.07451369613409042</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.02183043211698532</v>
+        <v>0.01801198162138462</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04970081895589828</v>
+        <v>0.1251330077648163</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.01914718002080917</v>
+        <v>0.01651190593838692</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.03731236606836319</v>
+        <v>0.1689947843551636</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0168917216360569</v>
+        <v>0.02043107710778713</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.03836708515882492</v>
+        <v>0.001477520912885666</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.009303104132413864</v>
+        <v>0.01012513972818851</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0006687622517347336</v>
+        <v>0.04388322308659554</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.01007444877177477</v>
+        <v>0.0432288832962513</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.01298626232892275</v>
+        <v>0.01869326829910278</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.05633450299501419</v>
+        <v>0.1407004743814468</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.06566191464662552</v>
+        <v>0.1083666086196899</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1452965140342712</v>
+        <v>0.1912916004657745</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01717729121446609</v>
+        <v>0.224409207701683</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.02943983301520348</v>
+        <v>0.07751888036727905</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.004001599736511707</v>
+        <v>0.02663760632276535</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.01876344159245491</v>
+        <v>0.2366362810134888</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.005811240524053574</v>
+        <v>0.1181528717279434</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.04853817448019981</v>
+        <v>0.07018192112445831</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.03951984643936157</v>
+        <v>0.0506758838891983</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.008180170319974422</v>
+        <v>0.02825932390987873</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04343339428305626</v>
+        <v>0.04323522001504898</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.02383989468216896</v>
+        <v>0.1004653126001358</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0551958829164505</v>
+        <v>0.02290748804807663</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.007302839774638414</v>
+        <v>0.07843863964080811</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.001529885688796639</v>
+        <v>0.06202707812190056</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.03532721847295761</v>
+        <v>0.2345622032880783</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.02667712233960629</v>
+        <v>0.01983003504574299</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.01805841736495495</v>
+        <v>0.02938761189579964</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.06214260682463646</v>
+        <v>0.1300537884235382</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.001239189994521439</v>
+        <v>0.04254848882555962</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0204000398516655</v>
+        <v>0.03340375795960426</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.01655999198555946</v>
+        <v>0.1040206253528595</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.006942142266780138</v>
+        <v>0.01167813967913389</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0002847108407877386</v>
+        <v>0.2449522018432617</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.01076498068869114</v>
+        <v>0.2220834642648697</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.005425759591162205</v>
+        <v>0.0668099969625473</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.03794269636273384</v>
+        <v>0.1393395364284515</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.01142008416354656</v>
+        <v>0.08321768045425415</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.005412241443991661</v>
+        <v>0.1114199906587601</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.008452590554952621</v>
+        <v>0.02153126150369644</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.02927767485380173</v>
+        <v>0.04632693529129028</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.008113354444503784</v>
+        <v>0.02008454501628876</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.01778021827340126</v>
+        <v>0.02398728393018246</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.003621118608862162</v>
+        <v>0.003583245910704136</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.01351530011743307</v>
+        <v>0.03461461886763573</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.02818246558308601</v>
+        <v>0.1154211238026619</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.01771636120975018</v>
+        <v>0.080905482172966</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.01560153439640999</v>
+        <v>0.2029690742492676</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.02700571157038212</v>
+        <v>0.0792793482542038</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.1062499433755875</v>
+        <v>0.09562409669160843</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.01229371223598719</v>
+        <v>0.06755178421735764</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.03548833355307579</v>
+        <v>0.02589066699147224</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.01191094517707825</v>
+        <v>0.05618992447853088</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.02378750033676624</v>
+        <v>0.007628357037901878</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04879606887698174</v>
+        <v>0.1521799713373184</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.00713513046503067</v>
+        <v>0.00490188505500555</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.02513999119400978</v>
+        <v>0.191237673163414</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0121740847826004</v>
+        <v>0.01666050776839256</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.03774886205792427</v>
+        <v>0.01088667381554842</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.01444150786846876</v>
+        <v>0.007500359788537025</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.001931591425091028</v>
+        <v>0.06551288813352585</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.01975887641310692</v>
+        <v>0.03940442204475403</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0155526390299201</v>
+        <v>0.06375586241483688</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.03110127337276936</v>
+        <v>0.07498881220817566</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.01703472994267941</v>
+        <v>0.09157656878232956</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.01578299887478352</v>
+        <v>0.07194245606660843</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01022402010858059</v>
+        <v>0.07883188873529434</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.008875114843249321</v>
+        <v>0.08058612048625946</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.001095008105039597</v>
+        <v>0.006533348932862282</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.03101265430450439</v>
+        <v>0.0308980792760849</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.02236615121364594</v>
+        <v>0.1496325880289078</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.01734625175595284</v>
+        <v>0.005302194505929947</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.007048201281577349</v>
+        <v>0.2469429224729538</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.005644898861646652</v>
+        <v>0.001885503530502319</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0281960740685463</v>
+        <v>0.07337146997451782</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.08213381469249725</v>
+        <v>0.2229172587394714</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.003397442400455475</v>
+        <v>0.02092797309160233</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.01373420096933842</v>
+        <v>0.02821374870836735</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.02692514844238758</v>
+        <v>0.1031023412942886</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.02661309763789177</v>
+        <v>0.09201347082853317</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.02935570478439331</v>
+        <v>0.007160724606364965</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01006100606173277</v>
+        <v>0.1013281270861626</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.006604801863431931</v>
+        <v>0.01671628654003143</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.008793001063168049</v>
+        <v>0.1458988934755325</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.008673769421875477</v>
+        <v>0.06868312507867813</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.04652156308293343</v>
+        <v>0.08379821479320526</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.07098656892776489</v>
+        <v>0.08479442447423935</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.02483117952942848</v>
+        <v>0.02791030704975128</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0255240760743618</v>
+        <v>0.02517083287239075</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2023859024047852</v>
+        <v>0.00145092885941267</v>
       </c>
       <c r="B3" t="n">
-        <v>1.760345339775085</v>
+        <v>0.09412344545125961</v>
       </c>
       <c r="C3" t="n">
-        <v>0.169800877571106</v>
+        <v>0.03126334026455879</v>
       </c>
       <c r="D3" t="n">
-        <v>1.012462496757507</v>
+        <v>0.1345320343971252</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4454622864723206</v>
+        <v>0.00225876085460186</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6598052382469177</v>
+        <v>0.04532796144485474</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06582251936197281</v>
+        <v>0.07919231802225113</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001903504133224487</v>
+        <v>0.06746141612529755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1607359796762466</v>
+        <v>0.03023663535714149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08295495808124542</v>
+        <v>0.01154530886560678</v>
       </c>
       <c r="K3" t="n">
-        <v>1.469298005104065</v>
+        <v>0.09419474750757217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005332822911441326</v>
+        <v>0.0287642814218998</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8757004141807556</v>
+        <v>0.1751010119915009</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5867722630500793</v>
+        <v>0.02311980724334717</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6810046434402466</v>
+        <v>0.02336264401674271</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2133021503686905</v>
+        <v>0.05993235111236572</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2652999758720398</v>
+        <v>0.01344059407711029</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2011615931987762</v>
+        <v>0.000234704464673996</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1032455489039421</v>
+        <v>0.003417377825826406</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2532499432563782</v>
+        <v>0.02130459062755108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04327839612960815</v>
+        <v>0.01146519742906094</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2086860984563828</v>
+        <v>0.01299170404672623</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0101077277213335</v>
+        <v>0.003877626731991768</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2600886225700378</v>
+        <v>0.01839638501405716</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.195720911026001</v>
+        <v>0.0005755056627094746</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2217555195093155</v>
+        <v>0.02059967443346977</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.223770946264267</v>
+        <v>0.02418096736073494</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1209676563739777</v>
+        <v>0.005561340134590864</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0471765547990799</v>
+        <v>0.006734190974384546</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.08020791411399841</v>
+        <v>0.01475051231682301</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1002658978104591</v>
+        <v>0.0610315315425396</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09051647782325745</v>
+        <v>0.002802499337121844</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1491631269454956</v>
+        <v>0.007980519905686378</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.07511237263679504</v>
+        <v>0.03502768278121948</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.07542677223682404</v>
+        <v>0.01854857057332993</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1475042402744293</v>
+        <v>0.02028808742761612</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.004600081592798233</v>
+        <v>0.0007465541129931808</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.3504495918750763</v>
+        <v>0.03535014763474464</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1144578009843826</v>
+        <v>0.003137511201202869</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.06816737353801727</v>
+        <v>0.02818374149501324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.04803486913442612</v>
+        <v>0.06337323784828186</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1089023724198341</v>
+        <v>0.02231763303279877</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.06735479831695557</v>
+        <v>0.03016383573412895</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.02545430511236191</v>
+        <v>0.009772611781954765</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1813095808029175</v>
+        <v>0.002142633311450481</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.4694548845291138</v>
+        <v>0.02303620800375938</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.198572754859924</v>
+        <v>0.0828624814748764</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1087570711970329</v>
+        <v>0.01106360740959644</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.4867599308490753</v>
+        <v>0.080159991979599</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.01966410130262375</v>
+        <v>0.008052097633481026</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1344010531902313</v>
+        <v>0.007017352618277073</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0559554286301136</v>
+        <v>0.02868611738085747</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.05846983194351196</v>
+        <v>0.008079608902335167</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1690346151590347</v>
+        <v>0.03184683993458748</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.08339492231607437</v>
+        <v>0.0133416261523962</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.2002098560333252</v>
+        <v>0.02085989527404308</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.3915432393550873</v>
+        <v>0.02100592479109764</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1821878850460052</v>
+        <v>0.003120945766568184</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.700065016746521</v>
+        <v>0.01192087307572365</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.2261956036090851</v>
+        <v>0.03677543997764587</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.2245175838470459</v>
+        <v>0.03699850291013718</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.09003699570894241</v>
+        <v>0.02829322963953018</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.2120295017957687</v>
+        <v>0.05403796955943108</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1396906226873398</v>
+        <v>0.006465169135481119</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03387926518917084</v>
+        <v>0.01952767372131348</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.125725656747818</v>
+        <v>0.01302730478346348</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.09320291131734848</v>
+        <v>0.003114372491836548</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.06870558857917786</v>
+        <v>0.02581100165843964</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1065185219049454</v>
+        <v>0.004547005519270897</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.03951911628246307</v>
+        <v>0.0238139946013689</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.06759384274482727</v>
+        <v>0.02505814470350742</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1188391447067261</v>
+        <v>0.004020847845822573</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.3101211786270142</v>
+        <v>0.009766119532287121</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.7270285487174988</v>
+        <v>0.06576219201087952</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1777305006980896</v>
+        <v>0.002866516122594476</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.2989145815372467</v>
+        <v>0.06727470457553864</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.09417741000652313</v>
+        <v>0.007905214093625546</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.09479382634162903</v>
+        <v>0.00766561646014452</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.05579401180148125</v>
+        <v>0.0003110654652118683</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1778902411460876</v>
+        <v>0.005555508658289909</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1545257270336151</v>
+        <v>0.0205688402056694</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.006940863095223904</v>
+        <v>0.0004450492560863495</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.248622938990593</v>
+        <v>0.03255409374833107</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1893881410360336</v>
+        <v>0.01387342624366283</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1679020673036575</v>
+        <v>0.04805012792348862</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.02390885353088379</v>
+        <v>0.006298546679317951</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1837694197893143</v>
+        <v>0.00236335932277143</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.07707930356264114</v>
+        <v>0.00718578090891242</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.04988893121480942</v>
+        <v>0.02556215226650238</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1215800046920776</v>
+        <v>0.01015428081154823</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.2522614002227783</v>
+        <v>0.0194072537124157</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.03139325976371765</v>
+        <v>0.04464719444513321</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.07842179387807846</v>
+        <v>0.003752380143851042</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.05234267562627792</v>
+        <v>0.08966327458620071</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1074938848614693</v>
+        <v>0.04135894030332565</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.006349427625536919</v>
+        <v>0.008545936085283756</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1885278820991516</v>
+        <v>0.02694501727819443</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1136502549052238</v>
+        <v>0.0124389985576272</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.06467415392398834</v>
+        <v>0.01868419907987118</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.006836296990513802</v>
+        <v>0.004442739766091108</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.225515678524971</v>
+        <v>0.03206358104944229</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.1761674582958221</v>
+        <v>0.01192990317940712</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.2067393511533737</v>
+        <v>0.05361179262399673</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.001781233586370945</v>
+        <v>0.004426593892276287</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2202654778957367</v>
+        <v>0.0002738721668720245</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.06329222768545151</v>
+        <v>0.009828101843595505</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.06901890784502029</v>
+        <v>0.01966922357678413</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.04471741616725922</v>
+        <v>0.01369550079107285</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.01695675030350685</v>
+        <v>0.01999594271183014</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1635337322950363</v>
+        <v>0.03627331554889679</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.007471202872693539</v>
+        <v>0.009164213202893734</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.8209132552146912</v>
+        <v>0.04642106592655182</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.3696761131286621</v>
+        <v>0.08717816323041916</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.08130438625812531</v>
+        <v>0.03872076421976089</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.03190835565328598</v>
+        <v>0.001418196596205235</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1280382871627808</v>
+        <v>0.02586755901575089</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0148109570145607</v>
+        <v>0.01507226284593344</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.05377612262964249</v>
+        <v>0.0003270006272941828</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.03172817453742027</v>
+        <v>0.008110020309686661</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.08667949587106705</v>
+        <v>0.006334898993372917</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.03039253316819668</v>
+        <v>0.02603021077811718</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1670348048210144</v>
+        <v>0.00330577022396028</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1502395421266556</v>
+        <v>0.007647647056728601</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1188410520553589</v>
+        <v>0.02317596971988678</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.004314934369176626</v>
+        <v>0.00935063511133194</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.2555947601795197</v>
+        <v>0.06263942271471024</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.03402046859264374</v>
+        <v>0.005298613104969263</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.08090738207101822</v>
+        <v>0.00219800416380167</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.2485054731369019</v>
+        <v>0.01580118946731091</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.2830855846405029</v>
+        <v>0.01649706065654755</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.08043219894170761</v>
+        <v>0.02114806324243546</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.004320435225963593</v>
+        <v>0.007039404474198818</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.02913534641265869</v>
+        <v>0.02303885109722614</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.09497561305761337</v>
+        <v>0.05108624696731567</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.04087897390127182</v>
+        <v>0.0593411847949028</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.08695697784423828</v>
+        <v>0.003654342610388994</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1746180504560471</v>
+        <v>0.03253495693206787</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.1843587011098862</v>
+        <v>0.000814367551356554</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.09964941442012787</v>
+        <v>0.04460644721984863</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0639641135931015</v>
+        <v>0.02823826298117638</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.2883372604846954</v>
+        <v>0.003998443484306335</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.06775009632110596</v>
+        <v>0.009831327944993973</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.04511376470327377</v>
+        <v>0.03148004412651062</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.01144313812255859</v>
+        <v>0.0005051521584391594</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.002755925059318542</v>
+        <v>0.007028092630207539</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1131688356399536</v>
+        <v>0.02670938707888126</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.2492786049842834</v>
+        <v>0.006676359102129936</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.1019013524055481</v>
+        <v>0.04172631353139877</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.02752804569900036</v>
+        <v>0.0046065803617239</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.4544576704502106</v>
+        <v>0.04614486545324326</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.07597693055868149</v>
+        <v>0.04178813099861145</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.2620256245136261</v>
+        <v>0.02696368470788002</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.003152196761220694</v>
+        <v>0.02384603396058083</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02252743393182755</v>
+        <v>0.001758498256094754</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2186736017465591</v>
+        <v>0.03582011535763741</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.11197280138731</v>
+        <v>0.01105310581624508</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2152421176433563</v>
+        <v>0.05754396691918373</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03927271068096161</v>
+        <v>0.006860998459160328</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.1994663029909134</v>
+        <v>0.005693208426237106</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.1052783727645874</v>
+        <v>0.01166932657361031</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.05477309972047806</v>
+        <v>0.0248495377600193</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.1076254844665527</v>
+        <v>0.0112742455676198</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01446115132421255</v>
+        <v>0.001008995342999697</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.2467895597219467</v>
+        <v>0.02479716762900352</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.0813886821269989</v>
+        <v>0.008502369746565819</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.08202626556158066</v>
+        <v>0.01676509901881218</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.04842884838581085</v>
+        <v>0.009614262729883194</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.04640959575772285</v>
+        <v>0.02676897123456001</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.01385602727532387</v>
+        <v>0.01708055101335049</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.1304664611816406</v>
+        <v>0.02307017333805561</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.08432602882385254</v>
+        <v>0.03549062833189964</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2942956984043121</v>
+        <v>0.007143992930650711</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.5987744331359863</v>
+        <v>0.05240027233958244</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.1553245186805725</v>
+        <v>0.001955213723704219</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.6942699551582336</v>
+        <v>0.01102112978696823</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1957343518733978</v>
+        <v>0.01798206567764282</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.1475764513015747</v>
+        <v>0.01058741100132465</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.1149302497506142</v>
+        <v>0.0008799168281257153</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.03592275828123093</v>
+        <v>0.01932021602988243</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.08259828388690948</v>
+        <v>0.006184268277138472</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.2586778700351715</v>
+        <v>0.007330357097089291</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.08384820818901062</v>
+        <v>0.0347246527671814</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1237035244703293</v>
+        <v>0.002872861921787262</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.09646599739789963</v>
+        <v>0.05887867510318756</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.1073767319321632</v>
+        <v>0.0137859545648098</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.02280598133802414</v>
+        <v>0.00373307429254055</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.6360382437705994</v>
+        <v>0.0472589023411274</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.05726077407598495</v>
+        <v>0.01037511043250561</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1041198819875717</v>
+        <v>0.004066984169185162</v>
       </c>
     </row>
     <row r="4">
@@ -2706,1140 +2706,1140 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0002617277204990387</v>
+        <v>0.04274788498878479</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001762598985806108</v>
+        <v>0.1985641866922379</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002669929817784578</v>
+        <v>0.06279755383729935</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003826389438472688</v>
+        <v>6.902217864990234e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007566412095911801</v>
+        <v>0.01494553126394749</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001257615629583597</v>
+        <v>0.2177845388650894</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001996539358515292</v>
+        <v>0.03318588435649872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0005483202985487878</v>
+        <v>0.07796457409858704</v>
       </c>
       <c r="I5" t="n">
-        <v>1.020986474031815e-05</v>
+        <v>0.03503086045384407</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002357150660827756</v>
+        <v>0.00773952528834343</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001656929962337017</v>
+        <v>0.2429612576961517</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001449263218091801</v>
+        <v>0.0844450369477272</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007889100816100836</v>
+        <v>0.05778256803750992</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000767940713558346</v>
+        <v>0.09703915566205978</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001460386556573212</v>
+        <v>0.230295717716217</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0004844660870730877</v>
+        <v>0.01859778724610806</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000138668532599695</v>
+        <v>0.019756143912673</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002050090843113139</v>
+        <v>0.03602819517254829</v>
       </c>
       <c r="S5" t="n">
-        <v>6.656919867964461e-05</v>
+        <v>0.002556517487391829</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003505237982608378</v>
+        <v>0.03482724726200104</v>
       </c>
       <c r="U5" t="n">
-        <v>2.394312286924105e-05</v>
+        <v>0.03787796199321747</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001673719380050898</v>
+        <v>0.07818181067705154</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002997523115482181</v>
+        <v>0.07380577921867371</v>
       </c>
       <c r="X5" t="n">
-        <v>6.310780008789152e-05</v>
+        <v>0.04068157449364662</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.00546001503244e-05</v>
+        <v>0.00306851789355278</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001884885132312775</v>
+        <v>0.02714821696281433</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000149839004734531</v>
+        <v>0.02748582325875759</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0004263315931893885</v>
+        <v>0.001856087706983089</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0003041295858565718</v>
+        <v>0.03480810672044754</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004275849205441773</v>
+        <v>0.02850962616503239</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0003304124111309648</v>
+        <v>0.06882181763648987</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0003296174108982086</v>
+        <v>0.09218945354223251</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0001304625620832667</v>
+        <v>0.04258444532752037</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0003162664943374693</v>
+        <v>0.006876847706735134</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.815518382703885e-05</v>
+        <v>0.1357539147138596</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001811514666769654</v>
+        <v>0.005232581868767738</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.018130857730284e-05</v>
+        <v>0.001786720938980579</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0004663227591663599</v>
+        <v>0.05748472362756729</v>
       </c>
       <c r="AM5" t="n">
-        <v>8.205587801057845e-05</v>
+        <v>0.0322720967233181</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.287056359928101e-05</v>
+        <v>0.04654843732714653</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0001807096996344626</v>
+        <v>0.01949595846235752</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.00011699727474479</v>
+        <v>0.02003973349928856</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0001812334812711924</v>
+        <v>0.01667273603379726</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.088962593115866e-05</v>
+        <v>0.04702454805374146</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.832591316197067e-05</v>
+        <v>0.04895887523889542</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0001320685405516997</v>
+        <v>0.01570279896259308</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001240753103047609</v>
+        <v>0.2644031941890717</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0002528411569073796</v>
+        <v>0.0545644611120224</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0003651712031569332</v>
+        <v>0.02048908174037933</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.866719483397901e-05</v>
+        <v>0.08080814033746719</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.813680086750537e-05</v>
+        <v>0.1369764059782028</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0006012528901919723</v>
+        <v>0.03350933268666267</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0001399435859639198</v>
+        <v>0.005168456118553877</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0001814683782868087</v>
+        <v>0.02890630066394806</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.765584137407131e-05</v>
+        <v>0.009282858110964298</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0003618684422690421</v>
+        <v>0.0425005778670311</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0003171882999595255</v>
+        <v>0.04193765670061111</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.983947681263089e-05</v>
+        <v>0.006121167913079262</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0007598722004331648</v>
+        <v>3.120210021734238e-05</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0007456766907125711</v>
+        <v>0.002185911405831575</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0002673538110684603</v>
+        <v>0.01826617866754532</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6.816821405664086e-05</v>
+        <v>0.0421023890376091</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0003175098972860724</v>
+        <v>0.007500936277210712</v>
       </c>
       <c r="BL5" t="n">
-        <v>7.588890730403364e-05</v>
+        <v>0.01733939908444881</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0003243006649427116</v>
+        <v>0.04133942723274231</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.507440851535648e-06</v>
+        <v>0.01085928734391928</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0002232995466329157</v>
+        <v>0.03315318003296852</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0003293874324299395</v>
+        <v>0.01889372617006302</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0001100087465601973</v>
+        <v>0.03074240311980247</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0002540548448450863</v>
+        <v>0.09830316156148911</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.683973434614018e-05</v>
+        <v>0.001242600148543715</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.375243563321419e-05</v>
+        <v>0.03819838166236877</v>
       </c>
       <c r="BU5" t="n">
-        <v>8.313293801620603e-05</v>
+        <v>0.01507354620844126</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0006642011576332152</v>
+        <v>0.154304563999176</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.547286026645452e-05</v>
+        <v>0.03487997502088547</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0001316123089054599</v>
+        <v>0.08395707607269287</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.00010344669863116</v>
+        <v>0.04511786252260208</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.804230305424426e-05</v>
+        <v>0.09395170956850052</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0003162069479003549</v>
+        <v>0.01597481966018677</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001030704152071849</v>
+        <v>0.000533323734998703</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.095179636147805e-05</v>
+        <v>0.03303797170519829</v>
       </c>
       <c r="CD5" t="n">
-        <v>9.175876039080322e-05</v>
+        <v>0.004697342868894339</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0002932156203314662</v>
+        <v>0.06967534869909286</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.271934135933407e-05</v>
+        <v>0.009733736515045166</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0001227735920110717</v>
+        <v>0.02094398066401482</v>
       </c>
       <c r="CH5" t="n">
-        <v>2.796902481350116e-05</v>
+        <v>0.0006093988195061684</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0002280095213791355</v>
+        <v>0.05122599005699158</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0002296059974469244</v>
+        <v>0.02543773874640465</v>
       </c>
       <c r="CK5" t="n">
-        <v>9.575270814821124e-05</v>
+        <v>0.0153410704806447</v>
       </c>
       <c r="CL5" t="n">
-        <v>3.985032526543364e-05</v>
+        <v>0.01713013276457787</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0002374572213739157</v>
+        <v>0.05174789577722549</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0002520753769204021</v>
+        <v>0.09854447096586227</v>
       </c>
       <c r="CO5" t="n">
-        <v>6.505403143819422e-05</v>
+        <v>0.06023463606834412</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0001215511292684823</v>
+        <v>0.06963817775249481</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0001804041530704126</v>
+        <v>0.04346224665641785</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0003457074053585529</v>
+        <v>0.00168485171161592</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0003700503730215132</v>
+        <v>0.04380989819765091</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.000519459368661046</v>
+        <v>0.00728957075625658</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0002121248544426635</v>
+        <v>0.0002828959841281176</v>
       </c>
       <c r="CV5" t="n">
-        <v>7.821789768058807e-05</v>
+        <v>0.008252508938312531</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0002444699348416179</v>
+        <v>0.05956113710999489</v>
       </c>
       <c r="CX5" t="n">
-        <v>4.266186806489713e-05</v>
+        <v>0.01428256276994944</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0001255151291843504</v>
+        <v>0.01201269403100014</v>
       </c>
       <c r="CZ5" t="n">
-        <v>8.263136987807229e-05</v>
+        <v>0.007153024431318045</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0002631066599860787</v>
+        <v>0.05710932612419128</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001561665121698752</v>
+        <v>0.01612225361168385</v>
       </c>
       <c r="DC5" t="n">
-        <v>4.191726111457683e-05</v>
+        <v>0.01303092297166586</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.408737080055289e-05</v>
+        <v>0.01473819091916084</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0001198632526211441</v>
+        <v>0.03463071584701538</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0003925043565686792</v>
+        <v>0.02193403616547585</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0005071883788332343</v>
+        <v>0.03982523083686829</v>
       </c>
       <c r="DH5" t="n">
-        <v>6.46121843601577e-05</v>
+        <v>0.00700078159570694</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.430868360330351e-05</v>
+        <v>0.03687978535890579</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0005122270085848868</v>
+        <v>0.0664091631770134</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.000308712013065815</v>
+        <v>0.01198296248912811</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0001356529392069206</v>
+        <v>0.05542153120040894</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0003928309597540647</v>
+        <v>0.006224688142538071</v>
       </c>
       <c r="DN5" t="n">
-        <v>7.377962174359709e-05</v>
+        <v>0.01631001010537148</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0001944709074450657</v>
+        <v>0.03310753405094147</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0002654303098097444</v>
+        <v>0.009839039295911789</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0004925079992972314</v>
+        <v>0.02825773693621159</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0002070651389658451</v>
+        <v>0.01654639840126038</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0005691631231456995</v>
+        <v>0.0175052098929882</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0003358086687512696</v>
+        <v>0.006139248609542847</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0002224878844572231</v>
+        <v>0.03525322303175926</v>
       </c>
       <c r="DV5" t="n">
-        <v>6.192425644258037e-05</v>
+        <v>0.02424080669879913</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.000236162799410522</v>
+        <v>0.02357620932161808</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.887597116176039e-05</v>
+        <v>0.01079647149890661</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0001962236419785768</v>
+        <v>0.03916829824447632</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0006533819250762463</v>
+        <v>0.03406269103288651</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0001271653163712472</v>
+        <v>0.004302022978663445</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0003021795128006488</v>
+        <v>0.06162579357624054</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0002441923716105521</v>
+        <v>0.002498541492968798</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0005047758459113538</v>
+        <v>0.0005827220156788826</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0002052104682661593</v>
+        <v>0.04541299492120743</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0001447909162379801</v>
+        <v>0.0009377682581543922</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0002582301385700703</v>
+        <v>0.007365813013166189</v>
       </c>
       <c r="EH5" t="n">
-        <v>5.780695119028678e-06</v>
+        <v>0.01504365541040897</v>
       </c>
       <c r="EI5" t="n">
-        <v>2.070207119686529e-05</v>
+        <v>0.06447025388479233</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0001870320847956464</v>
+        <v>0.02592779695987701</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0002144693717127666</v>
+        <v>0.02802845276892185</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0002440103562548757</v>
+        <v>0.003685468807816505</v>
       </c>
       <c r="EM5" t="n">
-        <v>6.280872912611812e-05</v>
+        <v>0.002986038802191615</v>
       </c>
       <c r="EN5" t="n">
-        <v>7.062698568915948e-05</v>
+        <v>0.01474350597709417</v>
       </c>
       <c r="EO5" t="n">
-        <v>5.760994827141985e-05</v>
+        <v>0.00337462592869997</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0001854629081208259</v>
+        <v>0.0372445210814476</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0002116493415087461</v>
+        <v>0.01855854876339436</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0001207240275107324</v>
+        <v>0.006150403060019016</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.000451684114523232</v>
+        <v>0.03360573947429657</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0001284317258978263</v>
+        <v>0.01956924796104431</v>
       </c>
       <c r="EU5" t="n">
-        <v>8.155331306625158e-05</v>
+        <v>0.01532371062785387</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0003294408670626581</v>
+        <v>0.01103513967245817</v>
       </c>
       <c r="EW5" t="n">
-        <v>4.353113763500005e-05</v>
+        <v>0.00261604180559516</v>
       </c>
       <c r="EX5" t="n">
-        <v>5.553531082114205e-05</v>
+        <v>0.0004288270138204098</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0002932226634584367</v>
+        <v>0.07288022339344025</v>
       </c>
       <c r="EZ5" t="n">
-        <v>4.280065695638768e-06</v>
+        <v>0.01185255497694016</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0001036132598528638</v>
+        <v>0.0123577993363142</v>
       </c>
       <c r="FB5" t="n">
-        <v>1.526812047814019e-05</v>
+        <v>0.004478046204894781</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0002246401272714138</v>
+        <v>0.05280914157629013</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.000211512902751565</v>
+        <v>0.02853348851203918</v>
       </c>
       <c r="FE5" t="n">
-        <v>4.031837306683883e-06</v>
+        <v>0.01463695336133242</v>
       </c>
       <c r="FF5" t="n">
-        <v>2.085640699078795e-05</v>
+        <v>0.0008782613440416753</v>
       </c>
       <c r="FG5" t="n">
-        <v>6.292364560067654e-05</v>
+        <v>0.001034172018989921</v>
       </c>
       <c r="FH5" t="n">
-        <v>5.601976590696722e-05</v>
+        <v>0.06643643975257874</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.000129214909975417</v>
+        <v>0.03512898460030556</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0004078516503795981</v>
+        <v>0.01400948874652386</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.000154285051394254</v>
+        <v>0.01588787510991096</v>
       </c>
       <c r="FL5" t="n">
-        <v>1.798495213733986e-05</v>
+        <v>0.06943174451589584</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0003459284198470414</v>
+        <v>0.03384136036038399</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0001814716670196503</v>
+        <v>0.09331504255533218</v>
       </c>
       <c r="FO5" t="n">
-        <v>6.836472311988473e-05</v>
+        <v>0.0633772537112236</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0001334823900833726</v>
+        <v>0.02037614211440086</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0007974430336616933</v>
+        <v>0.07934047281742096</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0002043439453700557</v>
+        <v>0.04853487759828568</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0002523029106669128</v>
+        <v>0.05357223004102707</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0003475053235888481</v>
+        <v>0.03708913922309875</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0002885283902287483</v>
+        <v>0.06764524430036545</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0006564304349012673</v>
+        <v>0.0170227587223053</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.000287065573502332</v>
+        <v>0.08751505613327026</v>
       </c>
       <c r="FX5" t="n">
-        <v>6.259203655645251e-05</v>
+        <v>0.03783002868294716</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.000213380204513669</v>
+        <v>0.02346868067979813</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0002120791468769312</v>
+        <v>0.005067612044513226</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0004126620478928089</v>
+        <v>0.04710423201322556</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0001845699007390067</v>
+        <v>0.009069499559700489</v>
       </c>
       <c r="GC5" t="n">
-        <v>8.644982881378382e-05</v>
+        <v>0.07691675424575806</v>
       </c>
       <c r="GD5" t="n">
-        <v>7.836417353246361e-05</v>
+        <v>0.06030585989356041</v>
       </c>
       <c r="GE5" t="n">
-        <v>6.011711957398802e-05</v>
+        <v>0.01779799163341522</v>
       </c>
       <c r="GF5" t="n">
-        <v>8.279685971501749e-06</v>
+        <v>0.01419948041439056</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0001202253915835172</v>
+        <v>0.03733616322278976</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0008056351216509938</v>
+        <v>0.3684241771697998</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03782788664102554</v>
+        <v>0.5056469440460205</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002771539147943258</v>
+        <v>0.0480915829539299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01760590076446533</v>
+        <v>0.04646874964237213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008760273456573486</v>
+        <v>0.01630955561995506</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03780140727758408</v>
+        <v>0.4615721702575684</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002824675757437944</v>
+        <v>0.09244799613952637</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01412805542349815</v>
+        <v>0.1922777593135834</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001853718305937946</v>
+        <v>0.1361053436994553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005563056096434593</v>
+        <v>0.3512128889560699</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0349176824092865</v>
+        <v>0.6405065059661865</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002012305427342653</v>
+        <v>0.07928036898374557</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01753167808055878</v>
+        <v>0.07385784387588501</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004228799138218164</v>
+        <v>0.22015580534935</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03629514202475548</v>
+        <v>0.4819891154766083</v>
       </c>
       <c r="P6" t="n">
-        <v>0.004992226604372263</v>
+        <v>0.1215360835194588</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005407496355473995</v>
+        <v>0.04952829331159592</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001111721503548324</v>
+        <v>0.242059126496315</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003289615502581</v>
+        <v>0.02370190806686878</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005296734161674976</v>
+        <v>0.07832897454500198</v>
       </c>
       <c r="U6" t="n">
-        <v>1.928815618157387e-05</v>
+        <v>0.09711681306362152</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001067849225364625</v>
+        <v>0.1903809607028961</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001794028066797182</v>
+        <v>0.1192519813776016</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0003801738785114139</v>
+        <v>0.1086773574352264</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002535415114834905</v>
+        <v>0.02133133634924889</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00260158721357584</v>
+        <v>0.2017495036125183</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003799139289185405</v>
+        <v>0.0820234939455986</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001060478389263153</v>
+        <v>0.1167286336421967</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.003661960363388062</v>
+        <v>0.1194359585642815</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.003296101931482553</v>
+        <v>0.05654007196426392</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.005608696490526199</v>
+        <v>0.1778172701597214</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001632378902286291</v>
+        <v>0.3064426481723785</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001409253338351846</v>
+        <v>0.09612054377794266</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.001992838922888041</v>
+        <v>0.0266825444996357</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.00285981991328299</v>
+        <v>0.1894682198762894</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0003951219841837883</v>
+        <v>0.04831349104642868</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.002324223984032869</v>
+        <v>0.1180256903171539</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.007760464213788509</v>
+        <v>0.1566746830940247</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001514512696303427</v>
+        <v>0.1146007180213928</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0008133462397381663</v>
+        <v>0.1239092946052551</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.00310101080685854</v>
+        <v>0.09889949858188629</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.005281271412968636</v>
+        <v>0.033907201141119</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.002398276934400201</v>
+        <v>0.07471964508295059</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.001364094205200672</v>
+        <v>0.1522051692008972</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.002887685550376773</v>
+        <v>0.1429110169410706</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.006094004027545452</v>
+        <v>0.2499417364597321</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.02879816479980946</v>
+        <v>0.4601344168186188</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.003655384294688702</v>
+        <v>0.08230705559253693</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.004411502275615931</v>
+        <v>0.04220305755734444</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.002068104688078165</v>
+        <v>0.1679091900587082</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.01559801772236824</v>
+        <v>0.2713358998298645</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.005446299910545349</v>
+        <v>0.018601194024086</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.002767134457826614</v>
+        <v>0.001680184621363878</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.004226378165185452</v>
+        <v>0.1297606974840164</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0029797931201756</v>
+        <v>0.04889420419931412</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.004140247125178576</v>
+        <v>0.0474449098110199</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.009570700116455555</v>
+        <v>0.08007586747407913</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.002919022459536791</v>
+        <v>0.0572580024600029</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01402500458061695</v>
+        <v>0.001101935282349586</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.015675975009799</v>
+        <v>0.1191649585962296</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.005379225593060255</v>
+        <v>0.03216880932450294</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.002051201183348894</v>
+        <v>0.05762013792991638</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.001801134436391294</v>
+        <v>0.06542056053876877</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0006104522035457194</v>
+        <v>0.01957434415817261</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.003646966069936752</v>
+        <v>0.01007078215479851</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.001295595429837704</v>
+        <v>0.004560644272714853</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.005066285375505686</v>
+        <v>0.06463281810283661</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.004346239846199751</v>
+        <v>0.01010215748101473</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0002968335465993732</v>
+        <v>0.06139001250267029</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.004292889963835478</v>
+        <v>0.2293202728033066</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0009349253959953785</v>
+        <v>0.04830429702997208</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.001298046088777483</v>
+        <v>0.09465257078409195</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.004214812535792589</v>
+        <v>0.0789305567741394</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0139039158821106</v>
+        <v>0.3080325126647949</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.001443522982299328</v>
+        <v>0.07646404206752777</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.004450342617928982</v>
+        <v>0.1364651620388031</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0007731475052423775</v>
+        <v>0.0745716467499733</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.006640238221734762</v>
+        <v>0.2493391335010529</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.002123465528711677</v>
+        <v>0.0001061074435710907</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.003642424941062927</v>
+        <v>0.06445391476154327</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.003421100554987788</v>
+        <v>0.09966601431369781</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0002218984009232372</v>
+        <v>0.05087818205356598</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.006578810978680849</v>
+        <v>0.1732605844736099</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.002787020057439804</v>
+        <v>0.02098995260894299</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.003986253868788481</v>
+        <v>0.02762548625469208</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0005117855034768581</v>
+        <v>0.02348246611654758</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006245820783078671</v>
+        <v>0.1450214236974716</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.003401679918169975</v>
+        <v>0.1052058190107346</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.001665729563683271</v>
+        <v>0.04812078177928925</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.002225792966783047</v>
+        <v>0.04266299307346344</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.005000372417271137</v>
+        <v>0.03858351707458496</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001105406903661788</v>
+        <v>0.2725740373134613</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0001663815055508167</v>
+        <v>0.06962116807699203</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.003052203450351954</v>
+        <v>0.1857435256242752</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00238599837757647</v>
+        <v>0.08802550286054611</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0007347865612246096</v>
+        <v>0.192963182926178</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.004800355061888695</v>
+        <v>0.03095955774188042</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.008304890245199203</v>
+        <v>0.02614050917327404</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0006296992069110274</v>
+        <v>0.006864335387945175</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0002657244622241706</v>
+        <v>0.03337936848402023</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.005066701676696539</v>
+        <v>0.1577736735343933</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.002659605583176017</v>
+        <v>0.02744672447443008</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.005288973450660706</v>
+        <v>0.0134333111345768</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0003503509797155857</v>
+        <v>0.007524414919316769</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.006756774615496397</v>
+        <v>0.1422683298587799</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.002988272346556187</v>
+        <v>0.07629023492336273</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.002883061766624451</v>
+        <v>0.07790248095989227</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0008762517245486379</v>
+        <v>0.04171805828809738</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.00194743718020618</v>
+        <v>0.04770998284220695</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.006205064710229635</v>
+        <v>0.04431309551000595</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.001526425592601299</v>
+        <v>0.0881342887878418</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.008042983710765839</v>
+        <v>0.05248367786407471</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.006716957781463861</v>
+        <v>0.2872670888900757</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.003130321158096194</v>
+        <v>0.05675574764609337</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.004410271998494864</v>
+        <v>0.01012317463755608</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.007835135795176029</v>
+        <v>0.06718067079782486</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.004294951912015676</v>
+        <v>0.1262279599905014</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0008835808839648962</v>
+        <v>0.04640001058578491</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.001047700876370072</v>
+        <v>0.1048993617296219</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.001128823263570666</v>
+        <v>0.06772793829441071</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.00628142524510622</v>
+        <v>1.356005668640137e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001575010130181909</v>
+        <v>0.05073916167020798</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.00476735457777977</v>
+        <v>0.1827629655599594</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.003682256443426013</v>
+        <v>0.05775142088532448</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0006430647918023169</v>
+        <v>0.2226361483335495</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.003273643320426345</v>
+        <v>0.04307795688509941</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0007864271756261587</v>
+        <v>0.08189526200294495</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.003397679654881358</v>
+        <v>0.02277187816798687</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.004058360122144222</v>
+        <v>0.04273786023259163</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.003750586183741689</v>
+        <v>0.1134069338440895</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.001128111965954304</v>
+        <v>0.2194472253322601</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001325385295785964</v>
+        <v>0.2290872186422348</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.001140007050707936</v>
+        <v>0.03206761926412582</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.001528984634205699</v>
+        <v>0.03084685280919075</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.001618301728740335</v>
+        <v>0.07885808497667313</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.003179119434207678</v>
+        <v>0.06019686162471771</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.005246887449175119</v>
+        <v>0.01358290947973728</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.002409378532320261</v>
+        <v>0.09004626423120499</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.00093794334679842</v>
+        <v>0.2056706249713898</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.002963659819215536</v>
+        <v>0.03724781051278114</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.005948066711425781</v>
+        <v>0.07162865996360779</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.004258354660123587</v>
+        <v>0.06213466078042984</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0006407997570931911</v>
+        <v>0.03722188994288445</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0005336962058208883</v>
+        <v>0.03986339643597603</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.140055246651173e-05</v>
+        <v>0.03720734268426895</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.005010377150028944</v>
+        <v>0.05736091360449791</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.002698170952498913</v>
+        <v>0.02915674820542336</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.002950357738882303</v>
+        <v>0.02032032981514931</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0015084930928424</v>
+        <v>0.01891227066516876</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.005619178060442209</v>
+        <v>0.1110989823937416</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.002132616471499205</v>
+        <v>0.03296542167663574</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.006123939529061317</v>
+        <v>0.05384489893913269</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.001211230992339551</v>
+        <v>0.1313600689172745</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0008123940788209438</v>
+        <v>0.04972962662577629</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.005683633964508772</v>
+        <v>0.1935281306505203</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.001271181856282055</v>
+        <v>0.01313954405486584</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.00442678015679121</v>
+        <v>0.01396398991346359</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0003382646827958524</v>
+        <v>0.0314975306391716</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.005968288518488407</v>
+        <v>0.1361992955207825</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.004026977811008692</v>
+        <v>0.0995117723941803</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.001542161917313933</v>
+        <v>0.0838705450296402</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.002104101702570915</v>
+        <v>0.01063437107950449</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.001158201834186912</v>
+        <v>0.005037693306803703</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.000336506636813283</v>
+        <v>0.2360890805721283</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.003586980514228344</v>
+        <v>0.1023169308900833</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.006959464401006699</v>
+        <v>0.03140533342957497</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0002991069050040096</v>
+        <v>0.08127040416002274</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0003552607959136367</v>
+        <v>0.1927638351917267</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.002255100989714265</v>
+        <v>0.08414578437805176</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.001806959975510836</v>
+        <v>0.338309109210968</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.002081318292766809</v>
+        <v>0.01029377058148384</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.001386850839480758</v>
+        <v>0.1214353814721107</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.01207691989839077</v>
+        <v>0.1749357581138611</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0009183722431771457</v>
+        <v>0.3238978385925293</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.006645652465522289</v>
+        <v>0.2400347292423248</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0008074963698163629</v>
+        <v>0.05886097252368927</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.00394379161298275</v>
+        <v>0.2033778131008148</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.002842324553057551</v>
+        <v>0.1009543761610985</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.001720852684229612</v>
+        <v>0.00746864452958107</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0005839915247634053</v>
+        <v>0.04790191724896431</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.004383702762424946</v>
+        <v>0.0687871128320694</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.003390423487871885</v>
+        <v>0.08567003905773163</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.001571624190546572</v>
+        <v>0.05872881785035133</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.00224628415890038</v>
+        <v>0.08203263580799103</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.004229470156133175</v>
+        <v>0.1616073846817017</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.002181077608838677</v>
+        <v>0.09503389894962311</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.009692296385765076</v>
+        <v>0.004831010475754738</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.001925039803609252</v>
+        <v>0.131237581372261</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.00118295312859118</v>
+        <v>0.1951426714658737</v>
       </c>
     </row>
     <row r="7">
@@ -4413,571 +4413,571 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00375024601817131</v>
+        <v>0.0008260436006821692</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09148687869310379</v>
+        <v>0.002221533330157399</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004894413286820054</v>
+        <v>3.581008058972657e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02830124273896217</v>
+        <v>0.000717008369974792</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006206422112882137</v>
+        <v>0.0002182314783567563</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08881412446498871</v>
+        <v>0.0008295701118186116</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005242731422185898</v>
+        <v>0.0002344287931919098</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04982241988182068</v>
+        <v>0.0006051153177395463</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01575643755495548</v>
+        <v>0.0001084384130081162</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001842917641624808</v>
+        <v>0.0005195307312533259</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08738499879837036</v>
+        <v>0.002399628749117255</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003153117373585701</v>
+        <v>9.491865057498217e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02962879836559296</v>
+        <v>0.0009945215424522758</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01381240040063858</v>
+        <v>0.0006793619832023978</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08430026471614838</v>
+        <v>0.001051084254868329</v>
       </c>
       <c r="P8" t="n">
-        <v>0.007422275841236115</v>
+        <v>1.626800076337531e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02042685076594353</v>
+        <v>0.0001686868345132098</v>
       </c>
       <c r="R8" t="n">
-        <v>0.007601179182529449</v>
+        <v>0.0006639724597334862</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001283388119190931</v>
+        <v>0.0001684536400716752</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002847305964678526</v>
+        <v>6.012359517626464e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.005915500223636627</v>
+        <v>0.0001450427662348375</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004473702516406775</v>
+        <v>0.0003162314824294299</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008910590782761574</v>
+        <v>0.0004494158201850951</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01209759805351496</v>
+        <v>0.0003457770799286664</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005115433130413294</v>
+        <v>0.0002809436700772494</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002964063081890345</v>
+        <v>0.0004369368543848395</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.007837334647774696</v>
+        <v>5.854043047293089e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004215957596898079</v>
+        <v>0.00016080129717011</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.00960383377969265</v>
+        <v>4.052725853398442e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01272660307586193</v>
+        <v>0.0001866366364993155</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002951062051579356</v>
+        <v>0.0007066182442940772</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0007755965925753117</v>
+        <v>0.00100701441988349</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.004484427161514759</v>
+        <v>0.0004246705211699009</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.00694189639762044</v>
+        <v>0.0001140002132160589</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.008068948984146118</v>
+        <v>0.0006137959426268935</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005273799877613783</v>
+        <v>1.848737520049326e-05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.008039994165301323</v>
+        <v>0.0002503896539565176</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01218121964484453</v>
+        <v>0.0004403948551043868</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.01178495958447456</v>
+        <v>0.0002712977875489742</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002126994542777538</v>
+        <v>0.00033748839632608</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.009905962273478508</v>
+        <v>8.4860366769135e-06</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0144480150192976</v>
+        <v>0.0001846136874519289</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.003796346019953489</v>
+        <v>0.0003754647332243621</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.009768973104655743</v>
+        <v>0.0001831177942221984</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002029669005423784</v>
+        <v>8.651894313516095e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00804318580776453</v>
+        <v>0.0004538943467196077</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.06681451201438904</v>
+        <v>0.001548255211673677</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.01798539236187935</v>
+        <v>0.0003194789169356227</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.009851288050413132</v>
+        <v>2.596927333797794e-05</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.01734971255064011</v>
+        <v>0.001071436563506722</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.02756176143884659</v>
+        <v>0.0006145296501927078</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.008040281943976879</v>
+        <v>2.745691381278448e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.01375571452081203</v>
+        <v>0.0002411986788501963</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001288731349632144</v>
+        <v>0.0002565612376201898</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.006814251188188791</v>
+        <v>0.0002527541073504835</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02305801585316658</v>
+        <v>0.0004426940868142992</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.01644292101264</v>
+        <v>0.000188289413927123</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0004015519516542554</v>
+        <v>0.000456280104117468</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.00397283211350441</v>
+        <v>0.000568972434848547</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.03840088844299316</v>
+        <v>0.000114213558845222</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.007427354343235493</v>
+        <v>1.871739732450806e-05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.005156612955033779</v>
+        <v>0.0002838771615643054</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.01003153435885906</v>
+        <v>0.0001456401951145381</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.00707085058093071</v>
+        <v>6.857370317447931e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001025006175041199</v>
+        <v>0.000157173431944102</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001275766175240278</v>
+        <v>8.624216570751742e-05</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0004006386734545231</v>
+        <v>3.917702997568995e-07</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.003325873520225286</v>
+        <v>0.0003615552559494972</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0006085566710680723</v>
+        <v>2.625296474434435e-06</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.003421045141294599</v>
+        <v>0.0005200018058530986</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.004615071229636669</v>
+        <v>0.0002228919620392844</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.005850448273122311</v>
+        <v>0.0003628727863542736</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.005934735760092735</v>
+        <v>0.0003046308120246977</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.03206705674529076</v>
+        <v>0.001040008501149714</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.01119045820087194</v>
+        <v>0.000162073876708746</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001439012354239821</v>
+        <v>0.0001573405170347542</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.00792448315769434</v>
+        <v>0.0002186849742429331</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01354040019214153</v>
+        <v>0.0006770365289412439</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.003897259477525949</v>
+        <v>0.0003214654861949384</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.007941404357552528</v>
+        <v>6.813558866269886e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003145574126392603</v>
+        <v>0.0001420479093212634</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.002246331190690398</v>
+        <v>0.0001826906373025849</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.01301323156803846</v>
+        <v>0.0006473019020631909</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001678036176599562</v>
+        <v>6.443759048124775e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003800991922616959</v>
+        <v>0.0001936731132445857</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005826839478686452</v>
+        <v>0.0001123329493566416</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01620902679860592</v>
+        <v>0.0002732149150688201</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.005661061033606529</v>
+        <v>0.0001113089165301062</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.007405407726764679</v>
+        <v>9.964605851564556e-05</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.002681230660527945</v>
+        <v>0.000162112875841558</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.005048720166087151</v>
+        <v>0.0004103961400687695</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01066877972334623</v>
+        <v>0.0008573223021812737</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.00210886774584651</v>
+        <v>0.0005024019628763199</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.01141163520514965</v>
+        <v>0.0004493106389418244</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.006815590895712376</v>
+        <v>5.722478090319782e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.00786612369120121</v>
+        <v>0.0004820706963073462</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.01275876816362143</v>
+        <v>8.68580536916852e-05</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.02250845730304718</v>
+        <v>0.0001660001289565116</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.008323264308273792</v>
+        <v>0.0001831323024816811</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001172719872556627</v>
+        <v>9.732926992001012e-05</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.01240891497582197</v>
+        <v>0.0006000623106956482</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0004870840348303318</v>
+        <v>4.528007411863655e-05</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.005906973965466022</v>
+        <v>0.0001938229106599465</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.001144767855294049</v>
+        <v>0.000132822257000953</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01779612526297569</v>
+        <v>0.0002920413971878588</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.003809162881225348</v>
+        <v>6.297853360592853e-06</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.00983726792037487</v>
+        <v>0.0002339846978429705</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0008731776615604758</v>
+        <v>0.0001220087797264569</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.00184824678581208</v>
+        <v>0.0002299108600709587</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.005966709926724434</v>
+        <v>0.0002658526645973325</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.008562617003917694</v>
+        <v>0.000142335906275548</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.02338405326008797</v>
+        <v>0.0003196954785380512</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01566803641617298</v>
+        <v>0.0008241867180913687</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01272042468190193</v>
+        <v>5.088222678750753e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.01007017027586699</v>
+        <v>0.0002201802853960544</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.01618912816047668</v>
+        <v>0.0001141201355494559</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.01339731458574533</v>
+        <v>5.061426782049239e-05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.006273376755416393</v>
+        <v>0.0001423608046025038</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001894312910735607</v>
+        <v>0.0004281594301573932</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0042215371504426</v>
+        <v>0.000192858453374356</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.004542337264865637</v>
+        <v>2.916971970989835e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.00147176266182214</v>
+        <v>0.0002869597519747913</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01048066094517708</v>
+        <v>0.0001932776212925091</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.00568688428029418</v>
+        <v>0.0001999779487960041</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.000578812207095325</v>
+        <v>0.0003941270406357944</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0008509809849783778</v>
+        <v>0.0001897269103210419</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.005163968540728092</v>
+        <v>0.0003001746081281453</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.005770547315478325</v>
+        <v>0.0001922018855111673</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.003495594020932913</v>
+        <v>0.0002823137037921697</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.003831490874290466</v>
+        <v>0.0003543207421898842</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.001189555274322629</v>
+        <v>9.110434621106833e-05</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.005104738287627697</v>
+        <v>2.172874519601464e-05</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.002393541159108281</v>
+        <v>7.397662557195872e-06</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.01011423300951719</v>
+        <v>0.0003287805011495948</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.009794640354812145</v>
+        <v>0.0002129381173290312</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.003805356100201607</v>
+        <v>2.411778405075893e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.01755840517580509</v>
+        <v>0.0001539853401482105</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.001038976712152362</v>
+        <v>0.0003023151657544076</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.006261146627366543</v>
+        <v>2.67494579020422e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.009761925786733627</v>
+        <v>1.259476630366407e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0119011215865612</v>
+        <v>0.0001502551167504862</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.003596539609134197</v>
+        <v>5.794453318230808e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0008825850673019886</v>
+        <v>0.0001935969048645347</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001166926929727197</v>
+        <v>7.627339073223993e-05</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.002613351447507739</v>
+        <v>0.0002919920661952347</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.01139204576611519</v>
+        <v>0.000357292388798669</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.005802905187010765</v>
+        <v>0.000110338005470112</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.001970337936654687</v>
+        <v>1.151441392721608e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.006229629274457693</v>
+        <v>0.0002389473374933004</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01420234236866236</v>
+        <v>0.0004171877517364919</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.003528183326125145</v>
+        <v>0.0001367878139717504</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01963607408106327</v>
+        <v>9.333822526969016e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.008049260824918747</v>
+        <v>0.0002235402789665386</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0006872960366308689</v>
+        <v>0.0001781889295671135</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.01087700482457876</v>
+        <v>0.0007092293817549944</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001216045115143061</v>
+        <v>4.128343425691128e-05</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.003237822325900197</v>
+        <v>0.0002257156738778576</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.001215678639709949</v>
+        <v>5.769704148406163e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.01389708369970322</v>
+        <v>0.0002307532558916137</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.004969707690179348</v>
+        <v>0.0001171651674667373</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.007009110413491726</v>
+        <v>0.0001551485620439053</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0006239037029445171</v>
+        <v>2.114962990162894e-05</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0002551475190557539</v>
+        <v>3.90623026760295e-05</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.005737762432545424</v>
+        <v>0.0004440981429070234</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.006876866333186626</v>
+        <v>0.000317199039272964</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.008031047880649567</v>
+        <v>0.0002313187578693032</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.00349160423502326</v>
+        <v>2.235058491351083e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.007807574700564146</v>
+        <v>0.0004583770642057061</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.002658498007804155</v>
+        <v>0.0002138889103662223</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.007508710026741028</v>
+        <v>0.000281177053693682</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.001109537901356816</v>
+        <v>0.0004335993726272136</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.007159503176808357</v>
+        <v>0.0005272391717880964</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.02157898060977459</v>
+        <v>0.0007926425896584988</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.009264823980629444</v>
+        <v>0.000482436444144696</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.008754041977226734</v>
+        <v>0.0005147329648025334</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.002955268602818251</v>
+        <v>0.0001184341963380575</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.001121076289564371</v>
+        <v>0.0004972799797542393</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.005336338188499212</v>
+        <v>0.0003192313306499273</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0009258594363927841</v>
+        <v>0.0001882825163193047</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.004723384045064449</v>
+        <v>0.0001360929454676807</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.005541567225009203</v>
+        <v>0.0002617259160615504</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01011181436479092</v>
+        <v>4.657777753891423e-05</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.005340956151485443</v>
+        <v>0.0003334850480314344</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.00712816696614027</v>
+        <v>9.823806612985209e-05</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.01783839054405689</v>
+        <v>5.181979213375598e-05</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.009362827986478806</v>
+        <v>0.0004576920182444155</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01270303782075644</v>
+        <v>0.0003244426043238491</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.009127555415034294</v>
+        <v>0.0002494744258001447</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.008123601786792278</v>
+        <v>0.0001646796154091135</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.02690247446298599</v>
+        <v>0.01019753143191338</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1686446964740753</v>
+        <v>0.0238927286118269</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04915449768304825</v>
+        <v>0.006440467666834593</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1062183603644371</v>
+        <v>0.006175252143293619</v>
       </c>
       <c r="E10" t="n">
-        <v>0.183856800198555</v>
+        <v>0.008439410477876663</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3414317071437836</v>
+        <v>0.05464399233460426</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01417484879493713</v>
+        <v>0.002081149257719517</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1389391422271729</v>
+        <v>0.04950248077511787</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05023272708058357</v>
+        <v>0.008190939202904701</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005745272152125835</v>
+        <v>0.008727054111659527</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1515150666236877</v>
+        <v>0.02442037686705589</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03311477228999138</v>
+        <v>0.001754708355292678</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07491686195135117</v>
+        <v>0.01383065432310104</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02906701155006886</v>
+        <v>0.001930044963955879</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2462079674005508</v>
+        <v>0.04915768653154373</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003614950925111771</v>
+        <v>0.008872362785041332</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1452090293169022</v>
+        <v>0.05822572112083435</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0356903001666069</v>
+        <v>0.01896366849541664</v>
       </c>
       <c r="S10" t="n">
-        <v>0.002344586886465549</v>
+        <v>0.001756012788973749</v>
       </c>
       <c r="T10" t="n">
-        <v>0.004764600656926632</v>
+        <v>0.00781055074185133</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02238180674612522</v>
+        <v>0.002516899956390262</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09107705950737</v>
+        <v>0.01190989464521408</v>
       </c>
       <c r="W10" t="n">
-        <v>0.06378824263811111</v>
+        <v>0.004189717117697001</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03550563752651215</v>
+        <v>0.002312871161848307</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03309474140405655</v>
+        <v>0.001547556254081428</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.02936672419309616</v>
+        <v>0.004827135242521763</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02468939125537872</v>
+        <v>0.002378985751420259</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00441092811524868</v>
+        <v>0.001489729387685657</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02347727864980698</v>
+        <v>0.002050310140475631</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.03165436536073685</v>
+        <v>0.003659685142338276</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001446879468858242</v>
+        <v>0.02198026701807976</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01037800870835781</v>
+        <v>0.02865820378065109</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01930292323231697</v>
+        <v>0.001133357407525182</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.06999681144952774</v>
+        <v>0.01609085500240326</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01987390965223312</v>
+        <v>0.003854142501950264</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02857067063450813</v>
+        <v>0.008365425281226635</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.008478001691401005</v>
+        <v>0.003095971420407295</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02767923101782799</v>
+        <v>0.009256746619939804</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.007884407415986061</v>
+        <v>0.008495057001709938</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02643218822777271</v>
+        <v>0.0007836490403860807</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.03859568014740944</v>
+        <v>0.01976414769887924</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.05728117749094963</v>
+        <v>0.02268329076468945</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.01509988121688366</v>
+        <v>0.006784086115658283</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.04639619588851929</v>
+        <v>0.003651005914434791</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0300904419273138</v>
+        <v>0.005910542327910662</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.02628983557224274</v>
+        <v>0.0006890548393130302</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.07283076643943787</v>
+        <v>0.06214817613363266</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.009351158514618874</v>
+        <v>0.005101587623357773</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.04078046232461929</v>
+        <v>0.003045990131795406</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1736070066690445</v>
+        <v>0.02386035770177841</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.2139889001846313</v>
+        <v>0.02132440730929375</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.01753287762403488</v>
+        <v>0.005623181350529194</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.05587676912546158</v>
+        <v>0.0004263615701347589</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.05806340277194977</v>
+        <v>0.01612578332424164</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.01856708154082298</v>
+        <v>0.00369202671572566</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.05609942227602005</v>
+        <v>0.04374512284994125</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.05070548504590988</v>
+        <v>0.01215062569826841</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.06204383447766304</v>
+        <v>0.004886164795607328</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.08877463638782501</v>
+        <v>0.05498028546571732</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.06587450951337814</v>
+        <v>0.0100103784352541</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.02870800904929638</v>
+        <v>0.005588424392044544</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.03077114932239056</v>
+        <v>0.004597917199134827</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.02527011558413506</v>
+        <v>0.00117582269012928</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0008584385504946113</v>
+        <v>0.005589007865637541</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05259690061211586</v>
+        <v>0.0001775235868990421</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.01615931466221809</v>
+        <v>0.01599747128784657</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.02405624836683273</v>
+        <v>0.003367481753230095</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01544687151908875</v>
+        <v>0.004408129490911961</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01186286844313145</v>
+        <v>0.006181560456752777</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.06300405412912369</v>
+        <v>0.004081880208104849</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.05475852638483047</v>
+        <v>0.01083298400044441</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.03457247465848923</v>
+        <v>6.467453204095364e-05</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01056982390582561</v>
+        <v>0.0001094560138881207</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05013888329267502</v>
+        <v>0.02770108357071877</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.003968924283981323</v>
+        <v>0.0009023742750287056</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.04360981658101082</v>
+        <v>0.00590844452381134</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.07289533317089081</v>
+        <v>0.01181676611304283</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.07412190735340118</v>
+        <v>0.02058239281177521</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0004928633570671082</v>
+        <v>0.005655601620674133</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0598190650343895</v>
+        <v>0.003243026789277792</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.02028989791870117</v>
+        <v>0.001537800533697009</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.008869385346770287</v>
+        <v>0.00167339516337961</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.02354214899241924</v>
+        <v>0.009838567115366459</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.000794336199760437</v>
+        <v>0.007926177233457565</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0278147179633379</v>
+        <v>0.004003117326647043</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01964504830539227</v>
+        <v>0.002716126618906856</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.05331768840551376</v>
+        <v>0.01521154493093491</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.008073383942246437</v>
+        <v>0.002378481905907393</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.02159163169562817</v>
+        <v>0.01128647848963737</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.00712252501398325</v>
+        <v>0.003896828275173903</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01050814241170883</v>
+        <v>0.003315014066174626</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.02388465404510498</v>
+        <v>0.00429469533264637</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.01306367106735706</v>
+        <v>0.01201480254530907</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0414721667766571</v>
+        <v>0.02105741761624813</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.1366500854492188</v>
+        <v>0.04842180013656616</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.02210958302021027</v>
+        <v>0.007326327264308929</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.03446544334292412</v>
+        <v>0.008134417235851288</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.02672111615538597</v>
+        <v>0.01828761398792267</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.05508602410554886</v>
+        <v>0.003168945200741291</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01368087902665138</v>
+        <v>0.001237130025401711</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.01697703450918198</v>
+        <v>0.007278884761035442</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.004779903683811426</v>
+        <v>0.005984821822494268</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02752741053700447</v>
+        <v>0.002611675765365362</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.03246766328811646</v>
+        <v>0.002317133825272322</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0620216391980648</v>
+        <v>0.01568069495260715</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.002384371124207973</v>
+        <v>0.000600203056819737</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.04007885605096817</v>
+        <v>0.007229621522128582</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.01001789141446352</v>
+        <v>0.002612030133605003</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.03418561443686485</v>
+        <v>0.01456733513623476</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.1046738475561142</v>
+        <v>0.02076741307973862</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.01065952889621258</v>
+        <v>0.00924014113843441</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.03783062100410461</v>
+        <v>0.01605778187513351</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1674755662679672</v>
+        <v>0.01956150121986866</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.1002722680568695</v>
+        <v>0.01015442050993443</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.04242398589849472</v>
+        <v>0.0130133181810379</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.09005659073591232</v>
+        <v>0.003267751773819327</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.1158613264560699</v>
+        <v>0.02857598103582859</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.01398939080536366</v>
+        <v>0.005846352782100439</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.002683879807591438</v>
+        <v>0.004334372468292713</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.02124653570353985</v>
+        <v>6.156181916594505e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.06280948221683502</v>
+        <v>0.007065135985612869</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.005697654094547033</v>
+        <v>0.002508220262825489</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.02091432176530361</v>
+        <v>0.008169367909431458</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.008914812467992306</v>
+        <v>0.003779669292271137</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.04921478033065796</v>
+        <v>0.00294588366523385</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0102539649233222</v>
+        <v>0.0007590855821035802</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0145431887358427</v>
+        <v>0.0003196411998942494</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.00712935347110033</v>
+        <v>0.002852421486750245</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01851977780461311</v>
+        <v>0.01184536889195442</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.03459853678941727</v>
+        <v>0.01307336799800396</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.04877007007598877</v>
+        <v>0.003754973877221346</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.03014891222119331</v>
+        <v>0.00194945465773344</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.01344911567866802</v>
+        <v>0.005464504007250071</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.04335441440343857</v>
+        <v>0.003763569518923759</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.05489079281687737</v>
+        <v>0.01571465469896793</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.02939289063215256</v>
+        <v>0.003014311892911792</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01251463405787945</v>
+        <v>5.065719597041607e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.02386038564145565</v>
+        <v>0.00352317956276238</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.002883940935134888</v>
+        <v>0.004815438762307167</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04363419488072395</v>
+        <v>0.007559666875749826</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.06885450333356857</v>
+        <v>0.0006380492122843862</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.01279390603303909</v>
+        <v>0.009459859691560268</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0161945428699255</v>
+        <v>0.01157130487263203</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.01909788697957993</v>
+        <v>0.003576491959393024</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01074324827641249</v>
+        <v>0.002901877742260695</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.01569491252303123</v>
+        <v>0.01483710668981075</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01310078892856836</v>
+        <v>6.941740866750479e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01719035021960735</v>
+        <v>0.00590863823890686</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.008391933515667915</v>
+        <v>0.008511775173246861</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.01293455436825752</v>
+        <v>0.01832576282322407</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001457367674447596</v>
+        <v>0.02106642536818981</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.08087988197803497</v>
+        <v>0.009528441354632378</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0165114514529705</v>
+        <v>0.0117780789732933</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01430554315447807</v>
+        <v>0.0003428782802075148</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01862087659537792</v>
+        <v>0.01071758754551411</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.01211665943264961</v>
+        <v>0.006304137408733368</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03107773885130882</v>
+        <v>0.002293504541739821</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.03622050583362579</v>
+        <v>0.001216418109834194</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.05726661160588264</v>
+        <v>0.01312777400016785</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.01273437775671482</v>
+        <v>0.001580022042617202</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.04401550441980362</v>
+        <v>0.009058913215994835</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.003061781637370586</v>
+        <v>0.0003838440170511603</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.009919805452227592</v>
+        <v>0.00304695894010365</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.02531911805272102</v>
+        <v>0.01581935025751591</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.03652261197566986</v>
+        <v>0.001945454394444823</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.03836160898208618</v>
+        <v>0.00597029784694314</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0186653845012188</v>
+        <v>0.002123076934367418</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.07466243207454681</v>
+        <v>0.01676136255264282</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.002911780029535294</v>
+        <v>0.003807255998253822</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.002776078879833221</v>
+        <v>0.003470940282568336</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.01716614328324795</v>
+        <v>5.955807864665985e-07</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.008522782474756241</v>
+        <v>0.000205503311008215</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.02483631856739521</v>
+        <v>0.03026409074664116</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.02042924053966999</v>
+        <v>0.04894767701625824</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01277043577283621</v>
+        <v>0.01314764842391014</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.1413556188344955</v>
+        <v>0.007646081037819386</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.07555630803108215</v>
+        <v>0.02493723668158054</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.06294478476047516</v>
+        <v>0.01639064401388168</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.03612536191940308</v>
+        <v>0.006610164884477854</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.02229710854589939</v>
+        <v>0.03136305138468742</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0138868996873498</v>
+        <v>0.0109718069434166</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.003175979014486074</v>
+        <v>0.006216810550540686</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.02272190526127815</v>
+        <v>0.001947846263647079</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.005739068612456322</v>
+        <v>0.005636535584926605</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1009225770831108</v>
+        <v>0.008750095963478088</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02212527394294739</v>
+        <v>0.001170734176412225</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.05161022767424583</v>
+        <v>0.001924865297041833</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.03811289742588997</v>
+        <v>0.0122876837849617</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.01128147169947624</v>
+        <v>0.006713860668241978</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.51459807966603e-05</v>
+        <v>4.445590207069472e-07</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0001700544089544564</v>
+        <v>2.644445339683443e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>1.201601025968557e-05</v>
+        <v>9.225758731190581e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>5.088582474854775e-05</v>
+        <v>4.493820597417653e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>5.767854418081697e-06</v>
+        <v>6.811857019783929e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001041287541738711</v>
+        <v>2.55190552707063e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>8.376808182219975e-06</v>
+        <v>4.335964831625461e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>5.706868250854313e-05</v>
+        <v>1.400241853843909e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>9.838602636591531e-06</v>
+        <v>3.242013690396561e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>2.081903039652389e-05</v>
+        <v>1.449787987439777e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001419392501702532</v>
+        <v>3.311540058348328e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>3.307864062662702e-06</v>
+        <v>1.463290573155973e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>7.335875125136226e-05</v>
+        <v>9.639119525672868e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>5.286173291096929e-06</v>
+        <v>7.211975116661051e-06</v>
       </c>
       <c r="O11" t="n">
-        <v>8.905927825253457e-05</v>
+        <v>2.614634831843432e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.091643182211556e-05</v>
+        <v>2.680731995496899e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.975095412693918e-05</v>
+        <v>1.195153163280338e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.847912128345342e-07</v>
+        <v>3.038858039872139e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>9.607239917386323e-06</v>
+        <v>6.194645720825065e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>1.649694968364201e-05</v>
+        <v>2.431544999126345e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>3.104112238361267e-06</v>
+        <v>5.536662683880422e-07</v>
       </c>
       <c r="V11" t="n">
-        <v>1.595183130120859e-05</v>
+        <v>3.964681582147023e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>2.745626989053562e-05</v>
+        <v>2.430003860354191e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>2.491696250217501e-06</v>
+        <v>8.868670192896388e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.371160119058914e-06</v>
+        <v>2.097069454976008e-06</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.12837731448235e-06</v>
+        <v>4.530080332187936e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.671573727435316e-06</v>
+        <v>6.99853444530163e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.856426024460234e-05</v>
+        <v>1.914761924126651e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.080106762354262e-05</v>
+        <v>2.96277698907943e-06</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.530825829831883e-05</v>
+        <v>2.595915702841012e-06</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44544701470295e-05</v>
+        <v>3.296162503829692e-06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.666303433012217e-06</v>
+        <v>6.797438345529372e-06</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.024777859332971e-05</v>
+        <v>5.666532160830684e-06</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.857545157690765e-06</v>
+        <v>2.14926467378973e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.344333188375458e-05</v>
+        <v>1.30893558889511e-05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.312199401581893e-06</v>
+        <v>3.325073294035974e-06</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.161255724786315e-05</v>
+        <v>2.297525043104542e-06</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.591828367963899e-05</v>
+        <v>7.309041393455118e-06</v>
       </c>
       <c r="AM11" t="n">
-        <v>7.87212593422737e-06</v>
+        <v>1.295619313168572e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.834332452854142e-06</v>
+        <v>4.960032129019964e-06</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.127603920598631e-06</v>
+        <v>1.2779739790858e-06</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.982184196298476e-05</v>
+        <v>3.682057467813138e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.160243664344307e-05</v>
+        <v>5.436090759758372e-07</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.841756056819577e-05</v>
+        <v>5.720055014535319e-06</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.804810709581943e-06</v>
+        <v>3.688203378260368e-06</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.867395258159377e-05</v>
+        <v>4.434776656125905e-06</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0001089293073164299</v>
+        <v>3.221602673875168e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.543884177925065e-06</v>
+        <v>3.886232207150897e-06</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.300973028468434e-05</v>
+        <v>4.556280146061908e-06</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.633363692439161e-05</v>
+        <v>1.388506734656403e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.626115984749049e-05</v>
+        <v>2.187250174756628e-05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9.771008990355767e-06</v>
+        <v>1.035681066241523e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.344997301406693e-05</v>
+        <v>3.415016863073106e-06</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.08855703426525e-06</v>
+        <v>3.661949904198991e-06</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.759725692973007e-06</v>
+        <v>1.433811803508434e-06</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.59529364889022e-05</v>
+        <v>7.908134648459964e-06</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.292248948127963e-05</v>
+        <v>6.649388069490669e-06</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.216496068285778e-05</v>
+        <v>1.893630496851983e-07</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.021189670311287e-05</v>
+        <v>9.97767347143963e-06</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.546355972299352e-05</v>
+        <v>1.831048621170339e-06</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.343737039860571e-05</v>
+        <v>4.441040346137015e-06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.05711387732299e-06</v>
+        <v>3.503020707285032e-06</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.027912912832107e-05</v>
+        <v>4.704267666966189e-06</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.797442109818803e-06</v>
+        <v>1.642593019823835e-06</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.936151577159762e-05</v>
+        <v>3.511416025503422e-06</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.494999014539644e-05</v>
+        <v>1.729619270918192e-06</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.685264214756899e-05</v>
+        <v>2.830420271493495e-07</v>
       </c>
       <c r="BP11" t="n">
-        <v>9.810071787796915e-06</v>
+        <v>1.423793833055242e-06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.491780717013171e-06</v>
+        <v>1.688828660917352e-06</v>
       </c>
       <c r="BR11" t="n">
-        <v>1.292753495363286e-05</v>
+        <v>3.241257218178362e-07</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.270518532692222e-05</v>
+        <v>6.168432946651592e-07</v>
       </c>
       <c r="BT11" t="n">
-        <v>3.920994458894711e-06</v>
+        <v>2.410036358924117e-06</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.786753091437276e-05</v>
+        <v>1.234115416082204e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.893826892133802e-05</v>
+        <v>1.615399014553986e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.20771228466765e-05</v>
+        <v>1.430296833859757e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>2.795059117488563e-07</v>
+        <v>4.859174623561557e-06</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.449799002439249e-06</v>
+        <v>5.725425126001937e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.383531293366104e-05</v>
+        <v>1.49632578541059e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.16811666986905e-06</v>
+        <v>4.074834123457549e-06</v>
       </c>
       <c r="CB11" t="n">
-        <v>1.765858178259805e-05</v>
+        <v>3.688810465973802e-06</v>
       </c>
       <c r="CC11" t="n">
-        <v>9.131623301072977e-06</v>
+        <v>5.329725354386028e-07</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.196911843086127e-06</v>
+        <v>6.024939125381934e-07</v>
       </c>
       <c r="CE11" t="n">
-        <v>2.894801218644716e-05</v>
+        <v>9.732205398904625e-06</v>
       </c>
       <c r="CF11" t="n">
-        <v>1.145732039731229e-05</v>
+        <v>1.75494062659709e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>1.461332158214645e-05</v>
+        <v>2.701689709283528e-06</v>
       </c>
       <c r="CH11" t="n">
-        <v>7.94615061749937e-06</v>
+        <v>5.779859293397749e-07</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.158354280050844e-05</v>
+        <v>5.796356617793208e-06</v>
       </c>
       <c r="CJ11" t="n">
-        <v>9.158898137684446e-06</v>
+        <v>1.234771360714149e-07</v>
       </c>
       <c r="CK11" t="n">
-        <v>6.034187208570074e-06</v>
+        <v>2.877003225876251e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>3.920112249033991e-06</v>
+        <v>8.495507017869386e-07</v>
       </c>
       <c r="CM11" t="n">
-        <v>3.932448453269899e-05</v>
+        <v>2.841805780917639e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.807752935041208e-05</v>
+        <v>6.980475518503226e-06</v>
       </c>
       <c r="CO11" t="n">
-        <v>8.454140697722323e-06</v>
+        <v>6.931591087777633e-06</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.350886759610148e-05</v>
+        <v>7.040184755169321e-06</v>
       </c>
       <c r="CQ11" t="n">
-        <v>1.013974906527437e-05</v>
+        <v>9.041422345035244e-06</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.626388620934449e-05</v>
+        <v>4.78860374641954e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>9.41719099500915e-06</v>
+        <v>7.649476856386173e-07</v>
       </c>
       <c r="CT11" t="n">
-        <v>1.569463347550482e-05</v>
+        <v>7.195828288786288e-07</v>
       </c>
       <c r="CU11" t="n">
-        <v>7.357773938565515e-06</v>
+        <v>3.00715328194201e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>5.003118076274404e-06</v>
+        <v>1.082713652067469e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.573238998593297e-05</v>
+        <v>8.451413123111706e-06</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.565513048262801e-05</v>
+        <v>3.092490715062013e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.664567571424413e-05</v>
+        <v>4.011982582596829e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>7.701412869209889e-06</v>
+        <v>1.347175498267461e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.291033004235942e-05</v>
+        <v>6.831332939327694e-06</v>
       </c>
       <c r="DB11" t="n">
-        <v>5.860841611138312e-06</v>
+        <v>1.000317297439324e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.257481380889658e-05</v>
+        <v>2.149382908100961e-06</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.216350251022959e-06</v>
+        <v>1.62058725550196e-07</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.564259036967997e-05</v>
+        <v>2.642591425683349e-07</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.721687087614555e-05</v>
+        <v>6.826221579103731e-06</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.48016835434828e-05</v>
+        <v>3.349745838931995e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>2.293452780577354e-05</v>
+        <v>1.588388158779708e-06</v>
       </c>
       <c r="DI11" t="n">
-        <v>1.989163138205186e-05</v>
+        <v>1.06456468529359e-06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>9.844718078966253e-06</v>
+        <v>1.060508566297358e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>2.396347190369852e-05</v>
+        <v>1.480658056607354e-06</v>
       </c>
       <c r="DL11" t="n">
-        <v>1.403611076966627e-05</v>
+        <v>1.081714162864955e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>2.150788532162551e-05</v>
+        <v>4.034172889078036e-06</v>
       </c>
       <c r="DN11" t="n">
-        <v>4.200080184091348e-06</v>
+        <v>2.092732529490604e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>4.282879672246054e-06</v>
+        <v>3.389000539755216e-06</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.845275947853224e-06</v>
+        <v>1.681240519246785e-06</v>
       </c>
       <c r="DQ11" t="n">
-        <v>1.574757152411621e-05</v>
+        <v>8.410183340856747e-07</v>
       </c>
       <c r="DR11" t="n">
-        <v>1.167740811069962e-05</v>
+        <v>8.716391448615468e-07</v>
       </c>
       <c r="DS11" t="n">
-        <v>8.143278137140442e-06</v>
+        <v>5.041278200224042e-06</v>
       </c>
       <c r="DT11" t="n">
-        <v>1.346079443464987e-05</v>
+        <v>3.782784915529191e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>8.069310752034653e-06</v>
+        <v>6.258235771383625e-06</v>
       </c>
       <c r="DV11" t="n">
-        <v>1.342740461041103e-06</v>
+        <v>5.594021672550298e-07</v>
       </c>
       <c r="DW11" t="n">
-        <v>4.703599188360386e-06</v>
+        <v>4.799862381332787e-06</v>
       </c>
       <c r="DX11" t="n">
-        <v>1.513390634499956e-05</v>
+        <v>5.235822754912078e-06</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.528372533561196e-06</v>
+        <v>5.275238891044864e-06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>8.028175216168165e-06</v>
+        <v>9.692408866612823e-07</v>
       </c>
       <c r="EA11" t="n">
-        <v>5.229861926636659e-06</v>
+        <v>5.333396529749734e-06</v>
       </c>
       <c r="EB11" t="n">
-        <v>3.813333478319691e-06</v>
+        <v>7.042780453048181e-06</v>
       </c>
       <c r="EC11" t="n">
-        <v>9.378841241414193e-06</v>
+        <v>2.981850684591336e-06</v>
       </c>
       <c r="ED11" t="n">
-        <v>1.554745267640101e-06</v>
+        <v>8.344050911546219e-06</v>
       </c>
       <c r="EE11" t="n">
-        <v>4.056697889609495e-06</v>
+        <v>6.977083558012964e-06</v>
       </c>
       <c r="EF11" t="n">
-        <v>9.154769031738397e-06</v>
+        <v>1.923799345604493e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>2.176888119720388e-05</v>
+        <v>4.453319888853002e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>2.194985245296266e-05</v>
+        <v>8.922368124331115e-07</v>
       </c>
       <c r="EI11" t="n">
-        <v>1.311003506998532e-05</v>
+        <v>7.13920144335134e-07</v>
       </c>
       <c r="EJ11" t="n">
-        <v>1.191153842228232e-07</v>
+        <v>2.205969849455869e-06</v>
       </c>
       <c r="EK11" t="n">
-        <v>1.240303481608862e-05</v>
+        <v>2.202726591349347e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>1.077467186405556e-05</v>
+        <v>1.388685859637917e-06</v>
       </c>
       <c r="EM11" t="n">
-        <v>3.50114561342707e-07</v>
+        <v>1.761909175002074e-06</v>
       </c>
       <c r="EN11" t="n">
-        <v>1.474817850066756e-06</v>
+        <v>8.585150794715446e-07</v>
       </c>
       <c r="EO11" t="n">
-        <v>4.946860826748889e-06</v>
+        <v>2.594386387499981e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>2.315966776222922e-05</v>
+        <v>4.09693438996328e-06</v>
       </c>
       <c r="EQ11" t="n">
-        <v>6.102955012465827e-06</v>
+        <v>4.806861966244469e-07</v>
       </c>
       <c r="ER11" t="n">
-        <v>2.289296389790252e-05</v>
+        <v>5.47224044566974e-06</v>
       </c>
       <c r="ES11" t="n">
-        <v>5.726652943849331e-06</v>
+        <v>3.457760612946004e-06</v>
       </c>
       <c r="ET11" t="n">
-        <v>5.506834895641077e-06</v>
+        <v>6.89752937432786e-07</v>
       </c>
       <c r="EU11" t="n">
-        <v>1.298923871217994e-05</v>
+        <v>5.436943979475473e-07</v>
       </c>
       <c r="EV11" t="n">
-        <v>1.844301368691958e-05</v>
+        <v>2.206657200076734e-06</v>
       </c>
       <c r="EW11" t="n">
-        <v>5.10812515130965e-06</v>
+        <v>4.668816018238431e-06</v>
       </c>
       <c r="EX11" t="n">
-        <v>9.076079550141003e-06</v>
+        <v>5.118614581078873e-07</v>
       </c>
       <c r="EY11" t="n">
-        <v>2.480171315255575e-05</v>
+        <v>1.046854413289111e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>8.308426913572475e-06</v>
+        <v>2.182964180974523e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>1.517356031399686e-05</v>
+        <v>3.309855401312234e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>8.278238965431228e-06</v>
+        <v>2.299760808455176e-07</v>
       </c>
       <c r="FC11" t="n">
-        <v>1.176850400952389e-05</v>
+        <v>7.056484719214495e-06</v>
       </c>
       <c r="FD11" t="n">
-        <v>1.076247826858889e-05</v>
+        <v>3.276143161201617e-07</v>
       </c>
       <c r="FE11" t="n">
-        <v>6.619293344556354e-06</v>
+        <v>2.829310915331007e-06</v>
       </c>
       <c r="FF11" t="n">
-        <v>7.536001248809043e-06</v>
+        <v>1.165321123153262e-06</v>
       </c>
       <c r="FG11" t="n">
-        <v>2.898896582337329e-06</v>
+        <v>1.559236807224806e-06</v>
       </c>
       <c r="FH11" t="n">
-        <v>2.626964942464838e-06</v>
+        <v>6.093012416386046e-06</v>
       </c>
       <c r="FI11" t="n">
-        <v>5.136819254403235e-06</v>
+        <v>3.076694838455296e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>3.557731179171242e-05</v>
+        <v>2.116858013323508e-06</v>
       </c>
       <c r="FK11" t="n">
-        <v>6.047735041647684e-06</v>
+        <v>2.778554289761814e-06</v>
       </c>
       <c r="FL11" t="n">
-        <v>1.581782453285996e-05</v>
+        <v>3.625767021731008e-06</v>
       </c>
       <c r="FM11" t="n">
-        <v>6.109883088356582e-06</v>
+        <v>1.2764351140504e-06</v>
       </c>
       <c r="FN11" t="n">
-        <v>9.230956493411213e-06</v>
+        <v>8.003768925846089e-06</v>
       </c>
       <c r="FO11" t="n">
-        <v>8.706084372533951e-06</v>
+        <v>8.336000973940827e-06</v>
       </c>
       <c r="FP11" t="n">
-        <v>1.662692920945119e-05</v>
+        <v>2.74438934866339e-06</v>
       </c>
       <c r="FQ11" t="n">
-        <v>3.057152935070917e-05</v>
+        <v>4.240105681674322e-06</v>
       </c>
       <c r="FR11" t="n">
-        <v>1.300495023315307e-05</v>
+        <v>7.350499799940735e-06</v>
       </c>
       <c r="FS11" t="n">
-        <v>3.196889520040713e-05</v>
+        <v>1.503318003415188e-06</v>
       </c>
       <c r="FT11" t="n">
-        <v>4.714133865491021e-06</v>
+        <v>3.137374733341858e-06</v>
       </c>
       <c r="FU11" t="n">
-        <v>6.953156116651371e-06</v>
+        <v>4.058707872900413e-06</v>
       </c>
       <c r="FV11" t="n">
-        <v>4.437056304595899e-07</v>
+        <v>7.376954272331204e-06</v>
       </c>
       <c r="FW11" t="n">
-        <v>5.989353667246178e-06</v>
+        <v>1.077991237252718e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>7.449117219948675e-06</v>
+        <v>7.08402967575239e-06</v>
       </c>
       <c r="FY11" t="n">
-        <v>2.036978366959374e-05</v>
+        <v>2.827131993399234e-06</v>
       </c>
       <c r="FZ11" t="n">
-        <v>1.20950262498809e-05</v>
+        <v>3.798587613346172e-07</v>
       </c>
       <c r="GA11" t="n">
-        <v>8.021002940949984e-06</v>
+        <v>8.525084922439419e-06</v>
       </c>
       <c r="GB11" t="n">
-        <v>1.56604471612809e-06</v>
+        <v>6.659125233454688e-07</v>
       </c>
       <c r="GC11" t="n">
-        <v>2.311144999112003e-05</v>
+        <v>1.031344709190307e-05</v>
       </c>
       <c r="GD11" t="n">
-        <v>1.4407738490263e-05</v>
+        <v>6.314468009804841e-06</v>
       </c>
       <c r="GE11" t="n">
-        <v>5.36162406206131e-05</v>
+        <v>2.201643383159535e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>1.009536845231196e-05</v>
+        <v>2.476517920513288e-06</v>
       </c>
       <c r="GG11" t="n">
-        <v>7.011029083514586e-06</v>
+        <v>2.871996912290342e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0004223206196911633</v>
+        <v>0.002622077241539955</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01160035841166973</v>
+        <v>0.2486110925674438</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0006499832961708307</v>
+        <v>0.1335588395595551</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004825339186936617</v>
+        <v>0.0371357835829258</v>
       </c>
       <c r="E12" t="n">
-        <v>0.006149595603346825</v>
+        <v>0.01498771086335182</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004554139450192451</v>
+        <v>0.1053254455327988</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0014787019463256</v>
+        <v>0.04946509748697281</v>
       </c>
       <c r="H12" t="n">
-        <v>4.777912545250729e-05</v>
+        <v>0.01173576712608337</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001053624087944627</v>
+        <v>0.1825170964002609</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000404518999857828</v>
+        <v>0.01352476142346859</v>
       </c>
       <c r="K12" t="n">
-        <v>0.009215713478624821</v>
+        <v>0.2677792906761169</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0009496726561337709</v>
+        <v>0.1411073505878448</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0006613538134843111</v>
+        <v>0.0216915886849165</v>
       </c>
       <c r="N12" t="n">
-        <v>0.003993990365415812</v>
+        <v>0.07684844732284546</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002763382392004132</v>
+        <v>0.08778755366802216</v>
       </c>
       <c r="P12" t="n">
-        <v>0.00287441024556756</v>
+        <v>0.06057462841272354</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001695675426162779</v>
+        <v>0.05160620808601379</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0003212782612536103</v>
+        <v>0.1502238810062408</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002283094945596531</v>
+        <v>0.004106749780476093</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0003294686903245747</v>
+        <v>0.05312735959887505</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0001786208886187524</v>
+        <v>0.05209127813577652</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001787130255252123</v>
+        <v>0.007905274629592896</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0003081509785261005</v>
+        <v>0.01022235956043005</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001055456814356148</v>
+        <v>0.06292697042226791</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.001153791206888855</v>
+        <v>0.01401375606656075</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0006269246223382652</v>
+        <v>0.003270439337939024</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.001584307407028973</v>
+        <v>0.07273036241531372</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.000364908657502383</v>
+        <v>0.06694035977125168</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0005096786771900952</v>
+        <v>0.02190567180514336</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.001566324615851045</v>
+        <v>0.0003608483821153641</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.00279945251531899</v>
+        <v>0.1136544123291969</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0008332019206136465</v>
+        <v>0.1348745226860046</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001249956316314638</v>
+        <v>0.03550994396209717</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0001078245259122923</v>
+        <v>0.02529584802687168</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.001735693775117397</v>
+        <v>0.002804928459227085</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0009787444723770022</v>
+        <v>0.113152913749218</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.000340278260409832</v>
+        <v>0.01210577785968781</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.001769058872014284</v>
+        <v>0.08663472533226013</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0006074659177102149</v>
+        <v>0.006962865591049194</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0004976668278686702</v>
+        <v>0.03241619467735291</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0001198829268105328</v>
+        <v>0.14100082218647</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.001441080356016755</v>
+        <v>0.04921639710664749</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0003824252926278859</v>
+        <v>0.001864994876086712</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.001106241601519287</v>
+        <v>0.01162919402122498</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0008707002853043377</v>
+        <v>0.01866233348846436</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.001536083174869418</v>
+        <v>0.02734344452619553</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.005453960504382849</v>
+        <v>0.2035261690616608</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001779614394763485</v>
+        <v>0.03136608004570007</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.004700347781181335</v>
+        <v>0.06547801196575165</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.004492169246077538</v>
+        <v>0.02322639152407646</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.003003129502758384</v>
+        <v>0.118965819478035</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.002030967269092798</v>
+        <v>0.01024108845740557</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0009815329685807228</v>
+        <v>0.05068421363830566</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.001976698404178023</v>
+        <v>0.09026359021663666</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.001095821266062558</v>
+        <v>0.03573048114776611</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.002380908001214266</v>
+        <v>0.03857601806521416</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.001121497247368097</v>
+        <v>0.08645717799663544</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0006121742771938443</v>
+        <v>0.04099735617637634</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.003755487035959959</v>
+        <v>0.06554944068193436</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.001408622600138187</v>
+        <v>0.05664309114217758</v>
       </c>
       <c r="BI12" t="n">
-        <v>7.478281622752547e-05</v>
+        <v>0.03104026429355145</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.001874816021881998</v>
+        <v>0.0103723555803299</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0009208099218085408</v>
+        <v>0.03429399058222771</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0002014416240854189</v>
+        <v>0.01913082040846348</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0008239144808612764</v>
+        <v>0.05541936308145523</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0009705058764666319</v>
+        <v>0.01678700000047684</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0005767678958363831</v>
+        <v>0.0827869176864624</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.002648659516125917</v>
+        <v>0.002065397799015045</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0008541335118934512</v>
+        <v>0.01441464107483625</v>
       </c>
       <c r="BR12" t="n">
-        <v>3.520370228216052e-05</v>
+        <v>0.02209166064858437</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.001663848175667226</v>
+        <v>0.02854344993829727</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0003149605181533843</v>
+        <v>0.03521639853715897</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.001362420036457479</v>
+        <v>0.01739443838596344</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.00385712506249547</v>
+        <v>0.1126040369272232</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001791560207493603</v>
+        <v>0.00560611579567194</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.001982835587114096</v>
+        <v>0.007504234090447426</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.002018815372139215</v>
+        <v>0.01883690990507603</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0006517710280604661</v>
+        <v>0.09249348193407059</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.001018916605971754</v>
+        <v>0.004670171067118645</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0004337157006375492</v>
+        <v>0.005713927559554577</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.001476173754781485</v>
+        <v>0.08469586819410324</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0003345420409459621</v>
+        <v>0.007239098660647869</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.001206378452479839</v>
+        <v>0.09940881282091141</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.000391998328268528</v>
+        <v>0.04736481234431267</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.00104657537303865</v>
+        <v>0.01323886401951313</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.000242871610680595</v>
+        <v>0.01111798919737339</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0007061115466058254</v>
+        <v>0.01560603268444538</v>
       </c>
       <c r="CJ12" t="n">
-        <v>3.251401358284056e-05</v>
+        <v>0.0003696158528327942</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0002929486217908561</v>
+        <v>0.009946884587407112</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.001047324854880571</v>
+        <v>0.03552554547786713</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0001401895424351096</v>
+        <v>0.02020561136305332</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.001584215206094086</v>
+        <v>0.1123999357223511</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0003255903138779104</v>
+        <v>0.0463913232088089</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.002974007045850158</v>
+        <v>0.1119881272315979</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0009558161254972219</v>
+        <v>0.1057923808693886</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.002317665610462427</v>
+        <v>0.144063875079155</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.002977244090288877</v>
+        <v>0.01060496736317873</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.001432217424735427</v>
+        <v>0.0008427519351243973</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.000334048381773755</v>
+        <v>0.007539710029959679</v>
       </c>
       <c r="CV12" t="n">
-        <v>5.540868369280361e-05</v>
+        <v>0.01525998674333096</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.001345907570794225</v>
+        <v>0.1016577631235123</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0006244274554774165</v>
+        <v>0.05105588212609291</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.001430190284736454</v>
+        <v>0.01327368896454573</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0005099985864944756</v>
+        <v>0.003534628544002771</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.001285691861994565</v>
+        <v>0.02991913259029388</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0003929357044398785</v>
+        <v>0.007898995652794838</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0004448109248187393</v>
+        <v>0.007814523763954639</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0008578253909945488</v>
+        <v>0.05835898220539093</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0005102570867165923</v>
+        <v>0.02292376384139061</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.002722127130255103</v>
+        <v>0.1275382488965988</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.000943482737056911</v>
+        <v>0.08287834376096725</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.006996933836489916</v>
+        <v>0.0160987600684166</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.004814473912119865</v>
+        <v>0.03979962319135666</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0003279551456216723</v>
+        <v>0.0529363751411438</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.002623461186885834</v>
+        <v>0.006875633262097836</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.003815325209870934</v>
+        <v>0.02480794675648212</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0005091829225420952</v>
+        <v>0.1193285882472992</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.001492546056397259</v>
+        <v>0.03760345280170441</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.001020149677060544</v>
+        <v>0.01890329644083977</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.00254571414552629</v>
+        <v>0.05570563301444054</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0006286570569500327</v>
+        <v>0.02802644483745098</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0007872374262660742</v>
+        <v>0.03493231907486916</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0009636167669668794</v>
+        <v>0.01328183710575104</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.000596493948251009</v>
+        <v>0.02554973214864731</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0006723471451550722</v>
+        <v>0.004382525570690632</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.001294857123866677</v>
+        <v>0.04676027223467827</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0005351077998057008</v>
+        <v>0.005747116636484861</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.999752753879875e-05</v>
+        <v>0.04425674676895142</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.001873909845016897</v>
+        <v>0.05002229288220406</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.001201820094138384</v>
+        <v>0.01030700094997883</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.000149184896145016</v>
+        <v>0.01119913998991251</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.000817020598333329</v>
+        <v>0.1071233525872231</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0004551748861558735</v>
+        <v>0.005241705104708672</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.001131098833866417</v>
+        <v>0.04392541199922562</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0008135361131280661</v>
+        <v>0.05781657993793488</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.001109770266339183</v>
+        <v>0.004939192906022072</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0007791600655764341</v>
+        <v>0.1137418448925018</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.00111237436067313</v>
+        <v>0.005021411925554276</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0004365990753285587</v>
+        <v>0.006500675342977047</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.001553335576318204</v>
+        <v>0.01955710723996162</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.001498680794611573</v>
+        <v>0.03204137831926346</v>
       </c>
       <c r="EL12" t="n">
-        <v>5.595052789431065e-05</v>
+        <v>0.01016498543322086</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0001129513839259744</v>
+        <v>0.006862998474389315</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0003825320454780012</v>
+        <v>0.05578659474849701</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.000182576070073992</v>
+        <v>0.01936308294534683</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0001096982014132664</v>
+        <v>0.05440285056829453</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.000308184971800074</v>
+        <v>0.001251286827027798</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0005315346643328667</v>
+        <v>0.005828684195876122</v>
       </c>
       <c r="ES12" t="n">
-        <v>7.490946154575795e-05</v>
+        <v>0.01026407163590193</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001965871080756187</v>
+        <v>0.01008625421673059</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0008279959438368678</v>
+        <v>0.0260743536055088</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.001169095281511545</v>
+        <v>0.0267214048653841</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0004144342383369803</v>
+        <v>0.02499599754810333</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0002215594431618229</v>
+        <v>0.008598968386650085</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.001247781910933554</v>
+        <v>0.1105989441275597</v>
       </c>
       <c r="EZ12" t="n">
-        <v>6.285163544816896e-05</v>
+        <v>0.05176401883363724</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.001203415566124022</v>
+        <v>0.02376847714185715</v>
       </c>
       <c r="FB12" t="n">
-        <v>3.922556061297655e-05</v>
+        <v>0.01026598270982504</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0009154790313914418</v>
+        <v>0.02801614813506603</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0002543339505791664</v>
+        <v>0.002161514014005661</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0002801390655804425</v>
+        <v>0.00399906886741519</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.001122780260629952</v>
+        <v>0.05420032888650894</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.000334064126946032</v>
+        <v>0.01242983154952526</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.001692102407105267</v>
+        <v>0.05786030739545822</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0004406615043990314</v>
+        <v>0.02879513427615166</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001949501456692815</v>
+        <v>0.01781412959098816</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0008935803198255599</v>
+        <v>0.00333537720143795</v>
       </c>
       <c r="FL12" t="n">
-        <v>5.59859472559765e-06</v>
+        <v>0.001957088708877563</v>
       </c>
       <c r="FM12" t="n">
-        <v>4.705216269940138e-05</v>
+        <v>0.01207189448177814</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.001377680222503841</v>
+        <v>0.01964752748608589</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0003309461171738803</v>
+        <v>0.07080411911010742</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0001419280888512731</v>
+        <v>0.07453738152980804</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.002596306847408414</v>
+        <v>0.11839859187603</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0004236062814015895</v>
+        <v>0.04325249418616295</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.002958928002044559</v>
+        <v>0.004347305744886398</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.002423906233161688</v>
+        <v>0.04163188859820366</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0007295706309378147</v>
+        <v>0.016710564494133</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.000658889242913574</v>
+        <v>0.02034800499677658</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0002426625724183396</v>
+        <v>0.07539971172809601</v>
       </c>
       <c r="FX12" t="n">
-        <v>3.196877878508531e-05</v>
+        <v>0.07082237303256989</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0002971923968289047</v>
+        <v>0.01100025232881308</v>
       </c>
       <c r="FZ12" t="n">
-        <v>2.539058914408088e-05</v>
+        <v>0.1035643219947815</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.000491468992549926</v>
+        <v>0.05243944376707077</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.001880722353234887</v>
+        <v>0.01037093997001648</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.003438549814745784</v>
+        <v>0.06025892496109009</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0006594194564968348</v>
+        <v>0.00224623829126358</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.003043293720111251</v>
+        <v>0.02828537113964558</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0003143726498819888</v>
+        <v>0.07165219634771347</v>
       </c>
       <c r="GG12" t="n">
-        <v>7.975644257385284e-05</v>
+        <v>0.05329766497015953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02012011408805847</v>
+        <v>9.90417756838724e-05</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2850244045257568</v>
+        <v>0.001016155467368662</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002078425139188766</v>
+        <v>9.229860734194517e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.145555391907692</v>
+        <v>0.0004767353821080178</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04121749103069305</v>
+        <v>0.000333216565195471</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2227675765752792</v>
+        <v>0.0008761611534282565</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008585946634411812</v>
+        <v>0.0004756704438477755</v>
       </c>
       <c r="H13" t="n">
-        <v>0.100689634680748</v>
+        <v>0.0007749556680209935</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01301836408674717</v>
+        <v>0.0001546000421512872</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05428391322493553</v>
+        <v>0.0001295583933824673</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2671616673469543</v>
+        <v>0.001199303078465164</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01096242386847734</v>
+        <v>0.0001446696842322126</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1025949493050575</v>
+        <v>0.0007411580299958587</v>
       </c>
       <c r="N13" t="n">
-        <v>0.004678701981902122</v>
+        <v>0.0007497791084460914</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2115422189235687</v>
+        <v>0.001192367170006037</v>
       </c>
       <c r="P13" t="n">
-        <v>0.009061485528945923</v>
+        <v>0.0003345804871059954</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04106967523694038</v>
+        <v>0.0004035554593428969</v>
       </c>
       <c r="R13" t="n">
-        <v>0.007997677661478519</v>
+        <v>0.0002941233396995813</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01367730274796486</v>
+        <v>0.0001047362529789098</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02207657694816589</v>
+        <v>7.618300151079893e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02566313371062279</v>
+        <v>0.00020587831386365</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03804104402661324</v>
+        <v>0.0001488000707468018</v>
       </c>
       <c r="W13" t="n">
-        <v>0.06662449985742569</v>
+        <v>0.0001643738360144198</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02402698621153831</v>
+        <v>0.0002043783897534013</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02144057862460613</v>
+        <v>0.000125243968795985</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.06557253003120422</v>
+        <v>0.0004538750217761844</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.04049178212881088</v>
+        <v>5.690921534551308e-05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.003801222890615463</v>
+        <v>0.0002134796231985092</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01052378676831722</v>
+        <v>0.0001769335940480232</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.008578258566558361</v>
+        <v>1.972115569515154e-05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01404701825231314</v>
+        <v>0.0003021008451469243</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01587991043925285</v>
+        <v>0.0001687636249698699</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01583826541900635</v>
+        <v>0.0003960671892855316</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01842003501951694</v>
+        <v>2.221762042609043e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01682115346193314</v>
+        <v>0.0008630788652226329</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01491383649408817</v>
+        <v>0.0001165542926173657</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02362013980746269</v>
+        <v>0.0001749207149259746</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.05347342044115067</v>
+        <v>7.83747382229194e-05</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.00344878900796175</v>
+        <v>0.0002193916880059987</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01013870630413294</v>
+        <v>0.0001049224301823415</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001384134870022535</v>
+        <v>0.0002035220677498728</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.03323651105165482</v>
+        <v>0.0001148018418462016</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.004499703180044889</v>
+        <v>8.484023419441655e-05</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01617760397493839</v>
+        <v>0.0004877686151303351</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.02977347187697887</v>
+        <v>8.108253678074107e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0422096773982048</v>
+        <v>0.0003304718993604183</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2055899500846863</v>
+        <v>0.0008386148838326335</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.007280693389475346</v>
+        <v>0.0002192101674154401</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.05830912292003632</v>
+        <v>0.0003265488485340029</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.02409946545958519</v>
+        <v>0.0008386177360080183</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.1192052811384201</v>
+        <v>0.0007071990403346717</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.03350852429866791</v>
+        <v>2.189688530052081e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.02713429369032383</v>
+        <v>0.0001594172790646553</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.06882734596729279</v>
+        <v>9.457259147893637e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.02535198256373405</v>
+        <v>6.955189019208774e-05</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04768793284893036</v>
+        <v>0.0004190174513496459</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.05411762744188309</v>
+        <v>8.231087122112513e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0008388389833271503</v>
+        <v>0.0003866491606459022</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03864405304193497</v>
+        <v>0.0005075698718428612</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.06730114668607712</v>
+        <v>0.0001096804262488149</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.02183896489441395</v>
+        <v>0.0001426580420229584</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.02251439541578293</v>
+        <v>0.0007174364291131496</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0171725507825613</v>
+        <v>2.751768261077814e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.001569731160998344</v>
+        <v>3.381727219675668e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.05944838374853134</v>
+        <v>0.0002584261819720268</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01237970683723688</v>
+        <v>4.05781865993049e-05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01362448837608099</v>
+        <v>7.330509833991528e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.003866259474307299</v>
+        <v>0.0002059398830169812</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.004267726093530655</v>
+        <v>2.217670771642588e-05</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.02373876981437206</v>
+        <v>0.0005780745414085686</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.01389953400939703</v>
+        <v>0.0002465319994371384</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.009481422603130341</v>
+        <v>9.751458128448576e-05</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0182272233068943</v>
+        <v>0.0001524837862234563</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1099521294236183</v>
+        <v>0.0003187821712344885</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.02040176652371883</v>
+        <v>0.0002146041806554422</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0443357527256012</v>
+        <v>0.0002179101720685139</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.02801880985498428</v>
+        <v>0.0002927962632384151</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0500844419002533</v>
+        <v>0.0003516183060128242</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01493652630597353</v>
+        <v>0.0001326314377365634</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0008676471188664436</v>
+        <v>0.0001369056117255241</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.04571563005447388</v>
+        <v>2.568190029705875e-05</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0004995991475880146</v>
+        <v>4.573430487653241e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.03857552632689476</v>
+        <v>0.0002968849730677903</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.02765863947570324</v>
+        <v>1.603722012077924e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.01838928461074829</v>
+        <v>0.0001489066344220191</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.007644719444215298</v>
+        <v>0.0001370062818750739</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03389562293887138</v>
+        <v>0.0002923175925388932</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.01952532306313515</v>
+        <v>0.0001239473203895614</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.01511551812291145</v>
+        <v>5.722796049667522e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.02459416911005974</v>
+        <v>9.839667472988367e-05</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.06178852915763855</v>
+        <v>0.0001013608634821139</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01328051835298538</v>
+        <v>0.0004210320767015219</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.008678850717842579</v>
+        <v>0.0005086094024591148</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.04967227205634117</v>
+        <v>0.0006045045447535813</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.004689502995461226</v>
+        <v>8.543232979718596e-06</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.007288048975169659</v>
+        <v>0.0003290991007816046</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.05686619505286217</v>
+        <v>0.0001198042373289354</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.05193591490387917</v>
+        <v>0.0002750156272668391</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.009712124243378639</v>
+        <v>0.0002427303115837276</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0007334635592997074</v>
+        <v>9.167096141027287e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.03452875837683678</v>
+        <v>0.0002648408699315041</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.02427602373063564</v>
+        <v>8.320699635078199e-06</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.03427808359265327</v>
+        <v>0.0002068086032522842</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.00995107926428318</v>
+        <v>9.852556831901893e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03556176647543907</v>
+        <v>0.0003337033849675208</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.02049705572426319</v>
+        <v>2.698706157389097e-05</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.02916504628956318</v>
+        <v>2.956220669148024e-05</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.01369003672152758</v>
+        <v>4.728881322080269e-05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.007203693967312574</v>
+        <v>0.0001355480053462088</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.01202398631721735</v>
+        <v>0.0001124151604017243</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.009672028943896294</v>
+        <v>0.0003463492321316153</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1061372011899948</v>
+        <v>0.0001039008202496916</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0562983863055706</v>
+        <v>0.0006827293545939028</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03624817356467247</v>
+        <v>0.0002655638090800494</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0001364094205200672</v>
+        <v>0.0001404961221851408</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.04429293423891068</v>
+        <v>0.0004094642063137144</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02632460743188858</v>
+        <v>0.0001966959971468896</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.005556501448154449</v>
+        <v>0.0001516791671747342</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001629330683499575</v>
+        <v>0.0002015519130509347</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.02258049696683884</v>
+        <v>0.0001286217739107087</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.001513317693024874</v>
+        <v>0.0001699243002803996</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.006857573520392179</v>
+        <v>2.907842281274498e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.005439832806587219</v>
+        <v>1.245731800736394e-05</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.003480215091258287</v>
+        <v>0.0002308225666638464</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.002919633407145739</v>
+        <v>0.0004554574261419475</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0218654815107584</v>
+        <v>0.0001048467456712388</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0003018621355295181</v>
+        <v>0.0001220591657329351</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0315123088657856</v>
+        <v>0.000115629707579501</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.02455930411815643</v>
+        <v>4.206273661111481e-05</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.01143795065581799</v>
+        <v>0.0003255006740801036</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.002982127014547586</v>
+        <v>0.0002669526729732752</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01746414788067341</v>
+        <v>0.0001445445523131639</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.001365927513688803</v>
+        <v>3.611263673519716e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.003541209734976292</v>
+        <v>0.0001685437164269388</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01550949458032846</v>
+        <v>0.0004430643166415393</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.01671620644629002</v>
+        <v>2.403727376076858e-05</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.04425378516316414</v>
+        <v>0.0001133146288339049</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.01475823111832142</v>
+        <v>0.000113645481178537</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0104115316644311</v>
+        <v>1.072721715900116e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.003301613731309772</v>
+        <v>0.0001334796252194792</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02198619581758976</v>
+        <v>0.0003475053235888481</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.01954195089638233</v>
+        <v>0.0001277283299714327</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.007582567632198334</v>
+        <v>1.644206895434763e-05</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.01353251654654741</v>
+        <v>7.020767952781171e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001389629207551479</v>
+        <v>9.275021147914231e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01938406750559807</v>
+        <v>0.0001407688832841814</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.02470463328063488</v>
+        <v>0.0002346533583477139</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02882634848356247</v>
+        <v>0.0001885856036096811</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01957403495907784</v>
+        <v>4.690166679210961e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.03271585702896118</v>
+        <v>0.0002865936257876456</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.04984380304813385</v>
+        <v>0.0001435314770787954</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0794650986790657</v>
+        <v>4.41088923253119e-05</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.007533925585448742</v>
+        <v>0.0001933383318828419</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.005941919982433319</v>
+        <v>0.0001000548800220713</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.033052708953619</v>
+        <v>0.0003833250957541168</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.02001914009451866</v>
+        <v>6.90052775098593e-06</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.02255402505397797</v>
+        <v>0.0002668059314601123</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.006923853419721127</v>
+        <v>8.830708975438029e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02930133789777756</v>
+        <v>0.0002844936971087009</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.03489171713590622</v>
+        <v>9.522432810626924e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.02063172310590744</v>
+        <v>1.904139207908884e-05</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.02581324055790901</v>
+        <v>1.111279743781779e-05</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.01207895949482918</v>
+        <v>6.440480501623824e-05</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01099297124892473</v>
+        <v>0.0003995001025032252</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.02396895363926888</v>
+        <v>0.0003408267511986196</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.03954622521996498</v>
+        <v>0.00018006467144005</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.008569457568228245</v>
+        <v>0.0002227339427918196</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0190498735755682</v>
+        <v>0.0001949848083313555</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.00270015699788928</v>
+        <v>0.0001910381542984396</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.02328494749963284</v>
+        <v>0.0002873990160878748</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.02029403299093246</v>
+        <v>0.0003788147587329149</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.02264255098998547</v>
+        <v>0.0002070073969662189</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.04473653808236122</v>
+        <v>9.174937440548092e-05</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.03484946489334106</v>
+        <v>0.000688027183059603</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0118772815912962</v>
+        <v>0.0002368695859331638</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.006335279904305935</v>
+        <v>0.0004886646056547761</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01213191449642181</v>
+        <v>8.836537745082751e-05</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.03453251719474792</v>
+        <v>4.512577288551256e-05</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.006351092364639044</v>
+        <v>0.000255766324698925</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01745818555355072</v>
+        <v>0.0001814593269955367</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.05729672312736511</v>
+        <v>2.986157414852642e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0179210752248764</v>
+        <v>0.0003890835214406252</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.03055831789970398</v>
+        <v>0.0003890349180437624</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01633109338581562</v>
+        <v>9.078110451810062e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01455988176167011</v>
+        <v>0.0005445434362627566</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.02308960445225239</v>
+        <v>0.0004597895313054323</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.1161069348454475</v>
+        <v>7.007413660176098e-05</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.002471242100000381</v>
+        <v>0.0001750827650539577</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.008502088487148285</v>
+        <v>0.000151219210238196</v>
       </c>
     </row>
     <row r="14">
